--- a/계산모델_엑셀/공정모델링_실험런시트_55런.xlsx
+++ b/계산모델_엑셀/공정모델링_실험런시트_55런.xlsx
@@ -71,10 +71,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -443,12 +443,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>목표: 모델을 한번 구축하면 [PD직경 D 입력] → [최적 kV·R·F·W 자동 결정] 되어 측정직경=100%·void 면적오차 ≤ ε·검사시간 최소 를 만족시키는 역설계 모델.</t>
+          <t>목표: 모델 구축 시 [PD직경 D 입력] → [최적 kV·R·F·W 자동 결정] 으로 측정직경=100%·void 면적오차≤ε·검사시간 최소.</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PD로 확인한 실제 범프 직경. 자재 고유·고정값(26·158µm). void 임계·N·bump면적의 '참값' 기준.</t>
+          <t>PD로 확인한 실제 범프 직경. 자재 고유·고정(26·158µm). N 설계·자재 구분의 기준.</t>
         </is>
       </c>
     </row>
@@ -502,71 +502,106 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>→ void% 는 '측정 bump면적'이 아니라 '고정 PD면적' 기준으로 계산. kV로 측정직경이 흔들려도 void 분모가 함께 흔들리지 않아 '같은 void'를 설정끼리 공정 비교 가능(최적점 측정직경=PD 에선 장비 void%와 일치).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>■ void% 기준 = '측정 bump면적' (실제 .csv 확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>XRA_VOID.csv 검증: 각 범프 Area = π/4·(측정직경)² 로 정확히 일치(오차 0.00). 즉 장비는 void%를 'void면적 ÷ 측정 bump면적'으로 계산하고 8% 판정도 여기에 적용. → 이 런시트는 장비가 출력한 void%를 그대로 입력(M열). 측정직경이 kV로 변하면 분모(측정면적)도 함께 변하지만, 운영점은 측정직경=PD(Q_dia=100%)라 그 지점에선 측정면적=PD면적.</t>
+        </is>
+      </c>
+    </row>
     <row r="9"/>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>■ 변수</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>독립변수</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>kV, R, F, W, PD직경 D(자재 2종)</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
+    <row r="11"/>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>종속변수</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>① 측정직경/PD=Q_dia ② void 절대면적→void%(PD) ③ void%σ ④ 매칭 성공</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>■ 각 독립변수의 void 측정 메커니즘</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>kV</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>대비 이동→경계 이동→void면적 변화(bias). 측정직경(=void% 분모)도 이동시켜 void%에 이중 작용.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>픽셀화 오차=2/N (N=0.283·PD직경/R). shot당 범프수·검사시간 ∝R².</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>두꺼운 범프 내부 광자부족→노이즈 void·경계 흔들림. 얇은 범프 둔감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>랜덤 노이즈 평균화(∝1/√F)→반복 σ. 시간 정비례.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>■ 설계 원리</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>교호작용(kV×R,W×F,×D) 존재 → OFAT 불가. [주효과 스윕 + 의심 교호작용 2×2 교차 + 같은범프 반복(σ)]. ε=10% 총예산 (2/N)²+(2σ)²≤10² → N_target≈29·σ≤3.5%(PD직경 기준). Ground truth 없어 자기참조(gold)+재현성으로 평가.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18"/>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>교호작용(kV×R,W×F,×D)→OFAT 불가. [주효과 스윕+의심 교호작용 2×2+같은범프 반복(σ)]. ε=10% 총예산 (2/N)²+(2σ)²≤10²→N_target≈29·σ≤3.5%. Ground truth 없어 자기참조(gold)+재현성 평가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="11">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A16:H18"/>
-    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="A8:H11"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="A7:H7"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="A20:H22"/>
     <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B15:H15"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="A7:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -578,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -594,12 +629,11 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -610,16 +644,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>직경 다이얼(kV)·void 픽셀화(R) 스윕. R최소(N58)행=gold → 그 void%(PD)를 O열에. 고정 kV스윕:gold R·F32·W4 / R스윕:kV*·F32·W4</t>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>직경 다이얼(kV)·void 픽셀화(R) 스윕. R최소(N58)행=gold → 그 void%를 N열에. 고정 kV스윕:gold R·F32·W4 / R스윕:kV*·F32·W4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속). void%(N열)=PD면적 기준 자동.</t>
+          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비 출력(측정면적 기준) 그대로 입력.</t>
         </is>
       </c>
     </row>
@@ -686,35 +720,30 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>void면적(절대,µm²)</t>
+          <t>void%(측정,장비값)</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>void%(PD기준)(자동)</t>
+          <t>기준gold void%</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>기준gold void%(PD)</t>
+          <t>void편차%(자동)</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>void편차%(자동)</t>
+          <t>판정(자동)</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>판정(자동)</t>
+          <t>tact(초)</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>tact(초)</t>
-        </is>
-      </c>
-      <c r="S5" s="6" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -757,19 +786,15 @@
         <f>IFERROR(J6/C6,"")</f>
         <v/>
       </c>
-      <c r="N6">
-        <f>IFERROR(M6/(0.7854*C6^2)*100,"")</f>
+      <c r="O6">
+        <f>IFERROR((M6-N6)/N6,"")</f>
         <v/>
       </c>
       <c r="P6">
-        <f>IFERROR((N6-O6)/O6,"")</f>
-        <v/>
-      </c>
-      <c r="Q6">
-        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(P6)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S6" t="inlineStr">
+        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>측정직경=PD 되는 kV* 찾기</t>
         </is>
@@ -812,19 +837,15 @@
         <f>IFERROR(J7/C7,"")</f>
         <v/>
       </c>
-      <c r="N7">
-        <f>IFERROR(M7/(0.7854*C7^2)*100,"")</f>
+      <c r="O7">
+        <f>IFERROR((M7-N7)/N7,"")</f>
         <v/>
       </c>
       <c r="P7">
-        <f>IFERROR((N7-O7)/O7,"")</f>
-        <v/>
-      </c>
-      <c r="Q7">
-        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(P7)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S7" t="inlineStr">
+        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>측정직경=PD 되는 kV* 찾기</t>
         </is>
@@ -867,19 +888,15 @@
         <f>IFERROR(J8/C8,"")</f>
         <v/>
       </c>
-      <c r="N8">
-        <f>IFERROR(M8/(0.7854*C8^2)*100,"")</f>
+      <c r="O8">
+        <f>IFERROR((M8-N8)/N8,"")</f>
         <v/>
       </c>
       <c r="P8">
-        <f>IFERROR((N8-O8)/O8,"")</f>
-        <v/>
-      </c>
-      <c r="Q8">
-        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(P8)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S8" t="inlineStr">
+        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>측정직경=PD 되는 kV* 찾기</t>
         </is>
@@ -922,19 +939,15 @@
         <f>IFERROR(J9/C9,"")</f>
         <v/>
       </c>
-      <c r="N9">
-        <f>IFERROR(M9/(0.7854*C9^2)*100,"")</f>
+      <c r="O9">
+        <f>IFERROR((M9-N9)/N9,"")</f>
         <v/>
       </c>
       <c r="P9">
-        <f>IFERROR((N9-O9)/O9,"")</f>
-        <v/>
-      </c>
-      <c r="Q9">
-        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(P9)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S9" t="inlineStr">
+        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>158µm kV* 찾기</t>
         </is>
@@ -977,19 +990,15 @@
         <f>IFERROR(J10/C10,"")</f>
         <v/>
       </c>
-      <c r="N10">
-        <f>IFERROR(M10/(0.7854*C10^2)*100,"")</f>
+      <c r="O10">
+        <f>IFERROR((M10-N10)/N10,"")</f>
         <v/>
       </c>
       <c r="P10">
-        <f>IFERROR((N10-O10)/O10,"")</f>
-        <v/>
-      </c>
-      <c r="Q10">
-        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(P10)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S10" t="inlineStr">
+        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>158µm kV* 찾기</t>
         </is>
@@ -1032,19 +1041,15 @@
         <f>IFERROR(J11/C11,"")</f>
         <v/>
       </c>
-      <c r="N11">
-        <f>IFERROR(M11/(0.7854*C11^2)*100,"")</f>
+      <c r="O11">
+        <f>IFERROR((M11-N11)/N11,"")</f>
         <v/>
       </c>
       <c r="P11">
-        <f>IFERROR((N11-O11)/O11,"")</f>
-        <v/>
-      </c>
-      <c r="Q11">
-        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(P11)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S11" t="inlineStr">
+        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>158µm kV* 찾기</t>
         </is>
@@ -1087,19 +1092,15 @@
         <f>IFERROR(J12/C12,"")</f>
         <v/>
       </c>
-      <c r="N12">
-        <f>IFERROR(M12/(0.7854*C12^2)*100,"")</f>
+      <c r="O12">
+        <f>IFERROR((M12-N12)/N12,"")</f>
         <v/>
       </c>
       <c r="P12">
-        <f>IFERROR((N12-O12)/O12,"")</f>
-        <v/>
-      </c>
-      <c r="Q12">
-        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(P12)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S12" t="inlineStr">
+        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(O12)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>N=58 =gold</t>
         </is>
@@ -1142,19 +1143,15 @@
         <f>IFERROR(J13/C13,"")</f>
         <v/>
       </c>
-      <c r="N13">
-        <f>IFERROR(M13/(0.7854*C13^2)*100,"")</f>
+      <c r="O13">
+        <f>IFERROR((M13-N13)/N13,"")</f>
         <v/>
       </c>
       <c r="P13">
-        <f>IFERROR((N13-O13)/O13,"")</f>
-        <v/>
-      </c>
-      <c r="Q13">
-        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(P13)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S13" t="inlineStr">
+        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(O13)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>N=29</t>
         </is>
@@ -1197,19 +1194,15 @@
         <f>IFERROR(J14/C14,"")</f>
         <v/>
       </c>
-      <c r="N14">
-        <f>IFERROR(M14/(0.7854*C14^2)*100,"")</f>
+      <c r="O14">
+        <f>IFERROR((M14-N14)/N14,"")</f>
         <v/>
       </c>
       <c r="P14">
-        <f>IFERROR((N14-O14)/O14,"")</f>
-        <v/>
-      </c>
-      <c r="Q14">
-        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(P14)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S14" t="inlineStr">
+        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(O14)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>N=14</t>
         </is>
@@ -1252,19 +1245,15 @@
         <f>IFERROR(J15/C15,"")</f>
         <v/>
       </c>
-      <c r="N15">
-        <f>IFERROR(M15/(0.7854*C15^2)*100,"")</f>
+      <c r="O15">
+        <f>IFERROR((M15-N15)/N15,"")</f>
         <v/>
       </c>
       <c r="P15">
-        <f>IFERROR((N15-O15)/O15,"")</f>
-        <v/>
-      </c>
-      <c r="Q15">
-        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(P15)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S15" t="inlineStr">
+        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(O15)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>N=58 =gold</t>
         </is>
@@ -1307,19 +1296,15 @@
         <f>IFERROR(J16/C16,"")</f>
         <v/>
       </c>
-      <c r="N16">
-        <f>IFERROR(M16/(0.7854*C16^2)*100,"")</f>
+      <c r="O16">
+        <f>IFERROR((M16-N16)/N16,"")</f>
         <v/>
       </c>
       <c r="P16">
-        <f>IFERROR((N16-O16)/O16,"")</f>
-        <v/>
-      </c>
-      <c r="Q16">
-        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(P16)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S16" t="inlineStr">
+        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(O16)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>N=29</t>
         </is>
@@ -1362,19 +1347,15 @@
         <f>IFERROR(J17/C17,"")</f>
         <v/>
       </c>
-      <c r="N17">
-        <f>IFERROR(M17/(0.7854*C17^2)*100,"")</f>
+      <c r="O17">
+        <f>IFERROR((M17-N17)/N17,"")</f>
         <v/>
       </c>
       <c r="P17">
-        <f>IFERROR((N17-O17)/O17,"")</f>
-        <v/>
-      </c>
-      <c r="Q17">
-        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(P17)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S17" t="inlineStr">
+        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(O17)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R17" t="inlineStr">
         <is>
           <t>N=14</t>
         </is>
@@ -1382,8 +1363,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:S3"/>
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:R3"/>
+    <mergeCell ref="A2:R2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1395,7 +1376,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1411,13 +1392,12 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1428,16 +1408,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>같은 범프 반복 → void%(PD) σ. 26µm=F스윕(W4), 158µm=W스윕(F32). 고정 kV*·R(N29).</t>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>같은 범프 반복→void% σ. 26µm=F스윕(W4), 158µm=W스윕(F32). 고정 kV*·R(N29).</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속). void%(N열)=PD면적 기준 자동.</t>
+          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비 출력(측정면적 기준) 그대로 입력.</t>
         </is>
       </c>
     </row>
@@ -1504,40 +1484,35 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>void면적(절대,µm²)</t>
+          <t>void%(측정,장비값)</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>void%(PD기준)(자동)</t>
+          <t>기준gold void%</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>기준gold void%(PD)</t>
+          <t>void편차%(자동)</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>void편차%(자동)</t>
+          <t>판정(자동)</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>판정(자동)</t>
+          <t>tact(초)</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>tact(초)</t>
+          <t>메모</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
-        <is>
-          <t>메모</t>
-        </is>
-      </c>
-      <c r="T5" s="6" t="inlineStr">
         <is>
           <t>void%σ_rel(자동)</t>
         </is>
@@ -1580,25 +1555,21 @@
         <f>IFERROR(J6/C6,"")</f>
         <v/>
       </c>
-      <c r="N6">
-        <f>IFERROR(M6/(0.7854*C6^2)*100,"")</f>
+      <c r="O6">
+        <f>IFERROR((M6-N6)/N6,"")</f>
         <v/>
       </c>
       <c r="P6">
-        <f>IFERROR((N6-O6)/O6,"")</f>
-        <v/>
-      </c>
-      <c r="Q6">
-        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(P6)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S6" t="inlineStr">
+        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>F=16 재현성</t>
         </is>
       </c>
-      <c r="T6">
-        <f>IFERROR(STDEV(N6:N8)/AVERAGE(N6:N8),"")</f>
+      <c r="S6">
+        <f>IFERROR(STDEV(M6:M8)/AVERAGE(M6:M8),"")</f>
         <v/>
       </c>
     </row>
@@ -1639,19 +1610,15 @@
         <f>IFERROR(J7/C7,"")</f>
         <v/>
       </c>
-      <c r="N7">
-        <f>IFERROR(M7/(0.7854*C7^2)*100,"")</f>
+      <c r="O7">
+        <f>IFERROR((M7-N7)/N7,"")</f>
         <v/>
       </c>
       <c r="P7">
-        <f>IFERROR((N7-O7)/O7,"")</f>
-        <v/>
-      </c>
-      <c r="Q7">
-        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(P7)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S7" t="inlineStr"/>
+        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1690,19 +1657,15 @@
         <f>IFERROR(J8/C8,"")</f>
         <v/>
       </c>
-      <c r="N8">
-        <f>IFERROR(M8/(0.7854*C8^2)*100,"")</f>
+      <c r="O8">
+        <f>IFERROR((M8-N8)/N8,"")</f>
         <v/>
       </c>
       <c r="P8">
-        <f>IFERROR((N8-O8)/O8,"")</f>
-        <v/>
-      </c>
-      <c r="Q8">
-        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(P8)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S8" t="inlineStr"/>
+        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1741,25 +1704,21 @@
         <f>IFERROR(J9/C9,"")</f>
         <v/>
       </c>
-      <c r="N9">
-        <f>IFERROR(M9/(0.7854*C9^2)*100,"")</f>
+      <c r="O9">
+        <f>IFERROR((M9-N9)/N9,"")</f>
         <v/>
       </c>
       <c r="P9">
-        <f>IFERROR((N9-O9)/O9,"")</f>
-        <v/>
-      </c>
-      <c r="Q9">
-        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(P9)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S9" t="inlineStr">
+        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>F=32 재현성</t>
         </is>
       </c>
-      <c r="T9">
-        <f>IFERROR(STDEV(N9:N11)/AVERAGE(N9:N11),"")</f>
+      <c r="S9">
+        <f>IFERROR(STDEV(M9:M11)/AVERAGE(M9:M11),"")</f>
         <v/>
       </c>
     </row>
@@ -1800,19 +1759,15 @@
         <f>IFERROR(J10/C10,"")</f>
         <v/>
       </c>
-      <c r="N10">
-        <f>IFERROR(M10/(0.7854*C10^2)*100,"")</f>
+      <c r="O10">
+        <f>IFERROR((M10-N10)/N10,"")</f>
         <v/>
       </c>
       <c r="P10">
-        <f>IFERROR((N10-O10)/O10,"")</f>
-        <v/>
-      </c>
-      <c r="Q10">
-        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(P10)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S10" t="inlineStr"/>
+        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1851,19 +1806,15 @@
         <f>IFERROR(J11/C11,"")</f>
         <v/>
       </c>
-      <c r="N11">
-        <f>IFERROR(M11/(0.7854*C11^2)*100,"")</f>
+      <c r="O11">
+        <f>IFERROR((M11-N11)/N11,"")</f>
         <v/>
       </c>
       <c r="P11">
-        <f>IFERROR((N11-O11)/O11,"")</f>
-        <v/>
-      </c>
-      <c r="Q11">
-        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(P11)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S11" t="inlineStr"/>
+        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1902,25 +1853,21 @@
         <f>IFERROR(J12/C12,"")</f>
         <v/>
       </c>
-      <c r="N12">
-        <f>IFERROR(M12/(0.7854*C12^2)*100,"")</f>
+      <c r="O12">
+        <f>IFERROR((M12-N12)/N12,"")</f>
         <v/>
       </c>
       <c r="P12">
-        <f>IFERROR((N12-O12)/O12,"")</f>
-        <v/>
-      </c>
-      <c r="Q12">
-        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(P12)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S12" t="inlineStr">
+        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(O12)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>F=64 재현성</t>
         </is>
       </c>
-      <c r="T12">
-        <f>IFERROR(STDEV(N12:N14)/AVERAGE(N12:N14),"")</f>
+      <c r="S12">
+        <f>IFERROR(STDEV(M12:M14)/AVERAGE(M12:M14),"")</f>
         <v/>
       </c>
     </row>
@@ -1961,19 +1908,15 @@
         <f>IFERROR(J13/C13,"")</f>
         <v/>
       </c>
-      <c r="N13">
-        <f>IFERROR(M13/(0.7854*C13^2)*100,"")</f>
+      <c r="O13">
+        <f>IFERROR((M13-N13)/N13,"")</f>
         <v/>
       </c>
       <c r="P13">
-        <f>IFERROR((N13-O13)/O13,"")</f>
-        <v/>
-      </c>
-      <c r="Q13">
-        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(P13)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S13" t="inlineStr"/>
+        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(O13)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2012,19 +1955,15 @@
         <f>IFERROR(J14/C14,"")</f>
         <v/>
       </c>
-      <c r="N14">
-        <f>IFERROR(M14/(0.7854*C14^2)*100,"")</f>
+      <c r="O14">
+        <f>IFERROR((M14-N14)/N14,"")</f>
         <v/>
       </c>
       <c r="P14">
-        <f>IFERROR((N14-O14)/O14,"")</f>
-        <v/>
-      </c>
-      <c r="Q14">
-        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(P14)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S14" t="inlineStr"/>
+        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(O14)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2063,25 +2002,21 @@
         <f>IFERROR(J15/C15,"")</f>
         <v/>
       </c>
-      <c r="N15">
-        <f>IFERROR(M15/(0.7854*C15^2)*100,"")</f>
+      <c r="O15">
+        <f>IFERROR((M15-N15)/N15,"")</f>
         <v/>
       </c>
       <c r="P15">
-        <f>IFERROR((N15-O15)/O15,"")</f>
-        <v/>
-      </c>
-      <c r="Q15">
-        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(P15)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S15" t="inlineStr">
+        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(O15)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>W=3 재현성·깜빡임</t>
         </is>
       </c>
-      <c r="T15">
-        <f>IFERROR(STDEV(N15:N17)/AVERAGE(N15:N17),"")</f>
+      <c r="S15">
+        <f>IFERROR(STDEV(M15:M17)/AVERAGE(M15:M17),"")</f>
         <v/>
       </c>
     </row>
@@ -2122,19 +2057,15 @@
         <f>IFERROR(J16/C16,"")</f>
         <v/>
       </c>
-      <c r="N16">
-        <f>IFERROR(M16/(0.7854*C16^2)*100,"")</f>
+      <c r="O16">
+        <f>IFERROR((M16-N16)/N16,"")</f>
         <v/>
       </c>
       <c r="P16">
-        <f>IFERROR((N16-O16)/O16,"")</f>
-        <v/>
-      </c>
-      <c r="Q16">
-        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(P16)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S16" t="inlineStr"/>
+        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(O16)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2173,19 +2104,15 @@
         <f>IFERROR(J17/C17,"")</f>
         <v/>
       </c>
-      <c r="N17">
-        <f>IFERROR(M17/(0.7854*C17^2)*100,"")</f>
+      <c r="O17">
+        <f>IFERROR((M17-N17)/N17,"")</f>
         <v/>
       </c>
       <c r="P17">
-        <f>IFERROR((N17-O17)/O17,"")</f>
-        <v/>
-      </c>
-      <c r="Q17">
-        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(P17)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S17" t="inlineStr"/>
+        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(O17)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2224,25 +2151,21 @@
         <f>IFERROR(J18/C18,"")</f>
         <v/>
       </c>
-      <c r="N18">
-        <f>IFERROR(M18/(0.7854*C18^2)*100,"")</f>
+      <c r="O18">
+        <f>IFERROR((M18-N18)/N18,"")</f>
         <v/>
       </c>
       <c r="P18">
-        <f>IFERROR((N18-O18)/O18,"")</f>
-        <v/>
-      </c>
-      <c r="Q18">
-        <f>IF(J18="","",IF(AND(L18="Y",K18&gt;=0.97,K18&lt;=1.03,IFERROR(ABS(P18)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S18" t="inlineStr">
+        <f>IF(J18="","",IF(AND(L18="Y",K18&gt;=0.97,K18&lt;=1.03,IFERROR(ABS(O18)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>W=4 재현성·깜빡임</t>
         </is>
       </c>
-      <c r="T18">
-        <f>IFERROR(STDEV(N18:N20)/AVERAGE(N18:N20),"")</f>
+      <c r="S18">
+        <f>IFERROR(STDEV(M18:M20)/AVERAGE(M18:M20),"")</f>
         <v/>
       </c>
     </row>
@@ -2283,19 +2206,15 @@
         <f>IFERROR(J19/C19,"")</f>
         <v/>
       </c>
-      <c r="N19">
-        <f>IFERROR(M19/(0.7854*C19^2)*100,"")</f>
+      <c r="O19">
+        <f>IFERROR((M19-N19)/N19,"")</f>
         <v/>
       </c>
       <c r="P19">
-        <f>IFERROR((N19-O19)/O19,"")</f>
-        <v/>
-      </c>
-      <c r="Q19">
-        <f>IF(J19="","",IF(AND(L19="Y",K19&gt;=0.97,K19&lt;=1.03,IFERROR(ABS(P19)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S19" t="inlineStr"/>
+        <f>IF(J19="","",IF(AND(L19="Y",K19&gt;=0.97,K19&lt;=1.03,IFERROR(ABS(O19)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2334,19 +2253,15 @@
         <f>IFERROR(J20/C20,"")</f>
         <v/>
       </c>
-      <c r="N20">
-        <f>IFERROR(M20/(0.7854*C20^2)*100,"")</f>
+      <c r="O20">
+        <f>IFERROR((M20-N20)/N20,"")</f>
         <v/>
       </c>
       <c r="P20">
-        <f>IFERROR((N20-O20)/O20,"")</f>
-        <v/>
-      </c>
-      <c r="Q20">
-        <f>IF(J20="","",IF(AND(L20="Y",K20&gt;=0.97,K20&lt;=1.03,IFERROR(ABS(P20)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S20" t="inlineStr"/>
+        <f>IF(J20="","",IF(AND(L20="Y",K20&gt;=0.97,K20&lt;=1.03,IFERROR(ABS(O20)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2385,25 +2300,21 @@
         <f>IFERROR(J21/C21,"")</f>
         <v/>
       </c>
-      <c r="N21">
-        <f>IFERROR(M21/(0.7854*C21^2)*100,"")</f>
+      <c r="O21">
+        <f>IFERROR((M21-N21)/N21,"")</f>
         <v/>
       </c>
       <c r="P21">
-        <f>IFERROR((N21-O21)/O21,"")</f>
-        <v/>
-      </c>
-      <c r="Q21">
-        <f>IF(J21="","",IF(AND(L21="Y",K21&gt;=0.97,K21&lt;=1.03,IFERROR(ABS(P21)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S21" t="inlineStr">
+        <f>IF(J21="","",IF(AND(L21="Y",K21&gt;=0.97,K21&lt;=1.03,IFERROR(ABS(O21)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R21" t="inlineStr">
         <is>
           <t>W=5 재현성·깜빡임</t>
         </is>
       </c>
-      <c r="T21">
-        <f>IFERROR(STDEV(N21:N23)/AVERAGE(N21:N23),"")</f>
+      <c r="S21">
+        <f>IFERROR(STDEV(M21:M23)/AVERAGE(M21:M23),"")</f>
         <v/>
       </c>
     </row>
@@ -2444,19 +2355,15 @@
         <f>IFERROR(J22/C22,"")</f>
         <v/>
       </c>
-      <c r="N22">
-        <f>IFERROR(M22/(0.7854*C22^2)*100,"")</f>
+      <c r="O22">
+        <f>IFERROR((M22-N22)/N22,"")</f>
         <v/>
       </c>
       <c r="P22">
-        <f>IFERROR((N22-O22)/O22,"")</f>
-        <v/>
-      </c>
-      <c r="Q22">
-        <f>IF(J22="","",IF(AND(L22="Y",K22&gt;=0.97,K22&lt;=1.03,IFERROR(ABS(P22)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S22" t="inlineStr"/>
+        <f>IF(J22="","",IF(AND(L22="Y",K22&gt;=0.97,K22&lt;=1.03,IFERROR(ABS(O22)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2495,19 +2402,15 @@
         <f>IFERROR(J23/C23,"")</f>
         <v/>
       </c>
-      <c r="N23">
-        <f>IFERROR(M23/(0.7854*C23^2)*100,"")</f>
+      <c r="O23">
+        <f>IFERROR((M23-N23)/N23,"")</f>
         <v/>
       </c>
       <c r="P23">
-        <f>IFERROR((N23-O23)/O23,"")</f>
-        <v/>
-      </c>
-      <c r="Q23">
-        <f>IF(J23="","",IF(AND(L23="Y",K23&gt;=0.97,K23&lt;=1.03,IFERROR(ABS(P23)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S23" t="inlineStr"/>
+        <f>IF(J23="","",IF(AND(L23="Y",K23&gt;=0.97,K23&lt;=1.03,IFERROR(ABS(O23)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2546,25 +2449,21 @@
         <f>IFERROR(J24/C24,"")</f>
         <v/>
       </c>
-      <c r="N24">
-        <f>IFERROR(M24/(0.7854*C24^2)*100,"")</f>
+      <c r="O24">
+        <f>IFERROR((M24-N24)/N24,"")</f>
         <v/>
       </c>
       <c r="P24">
-        <f>IFERROR((N24-O24)/O24,"")</f>
-        <v/>
-      </c>
-      <c r="Q24">
-        <f>IF(J24="","",IF(AND(L24="Y",K24&gt;=0.97,K24&lt;=1.03,IFERROR(ABS(P24)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S24" t="inlineStr">
+        <f>IF(J24="","",IF(AND(L24="Y",K24&gt;=0.97,K24&lt;=1.03,IFERROR(ABS(O24)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R24" t="inlineStr">
         <is>
           <t>W=6 재현성·깜빡임</t>
         </is>
       </c>
-      <c r="T24">
-        <f>IFERROR(STDEV(N24:N26)/AVERAGE(N24:N26),"")</f>
+      <c r="S24">
+        <f>IFERROR(STDEV(M24:M26)/AVERAGE(M24:M26),"")</f>
         <v/>
       </c>
     </row>
@@ -2605,19 +2504,15 @@
         <f>IFERROR(J25/C25,"")</f>
         <v/>
       </c>
-      <c r="N25">
-        <f>IFERROR(M25/(0.7854*C25^2)*100,"")</f>
+      <c r="O25">
+        <f>IFERROR((M25-N25)/N25,"")</f>
         <v/>
       </c>
       <c r="P25">
-        <f>IFERROR((N25-O25)/O25,"")</f>
-        <v/>
-      </c>
-      <c r="Q25">
-        <f>IF(J25="","",IF(AND(L25="Y",K25&gt;=0.97,K25&lt;=1.03,IFERROR(ABS(P25)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S25" t="inlineStr"/>
+        <f>IF(J25="","",IF(AND(L25="Y",K25&gt;=0.97,K25&lt;=1.03,IFERROR(ABS(O25)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2656,24 +2551,20 @@
         <f>IFERROR(J26/C26,"")</f>
         <v/>
       </c>
-      <c r="N26">
-        <f>IFERROR(M26/(0.7854*C26^2)*100,"")</f>
+      <c r="O26">
+        <f>IFERROR((M26-N26)/N26,"")</f>
         <v/>
       </c>
       <c r="P26">
-        <f>IFERROR((N26-O26)/O26,"")</f>
-        <v/>
-      </c>
-      <c r="Q26">
-        <f>IF(J26="","",IF(AND(L26="Y",K26&gt;=0.97,K26&lt;=1.03,IFERROR(ABS(P26)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S26" t="inlineStr"/>
+        <f>IF(J26="","",IF(AND(L26="Y",K26&gt;=0.97,K26&lt;=1.03,IFERROR(ABS(O26)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R26" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:S3"/>
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:R3"/>
+    <mergeCell ref="A2:R2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2685,7 +2576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2701,13 +2592,12 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2718,16 +2608,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>의심 교호작용 교차. kV×R(26µm): 대비bias×픽셀화 / W×F(158µm): SNR∝√(W·F) 교환. ×D는 두 자재로 확인.</t>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>kV×R(26µm): 대비bias×픽셀화 / W×F(158µm): SNR∝√(W·F) 교환. ×D는 두 자재로 확인.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속). void%(N열)=PD면적 기준 자동.</t>
+          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비 출력(측정면적 기준) 그대로 입력.</t>
         </is>
       </c>
     </row>
@@ -2794,40 +2684,35 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>void면적(절대,µm²)</t>
+          <t>void%(측정,장비값)</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>void%(PD기준)(자동)</t>
+          <t>기준gold void%</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>기준gold void%(PD)</t>
+          <t>void편차%(자동)</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>void편차%(자동)</t>
+          <t>판정(자동)</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>판정(자동)</t>
+          <t>tact(초)</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>tact(초)</t>
+          <t>메모</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
-        <is>
-          <t>메모</t>
-        </is>
-      </c>
-      <c r="T5" s="6" t="inlineStr">
         <is>
           <t>void%σ_rel(자동)</t>
         </is>
@@ -2870,25 +2755,21 @@
         <f>IFERROR(J6/C6,"")</f>
         <v/>
       </c>
-      <c r="N6">
-        <f>IFERROR(M6/(0.7854*C6^2)*100,"")</f>
+      <c r="O6">
+        <f>IFERROR((M6-N6)/N6,"")</f>
         <v/>
       </c>
       <c r="P6">
-        <f>IFERROR((N6-O6)/O6,"")</f>
-        <v/>
-      </c>
-      <c r="Q6">
-        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(P6)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S6" t="inlineStr">
+        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>kV55.5×N14</t>
         </is>
       </c>
-      <c r="T6">
-        <f>IFERROR(STDEV(N6:N7)/AVERAGE(N6:N7),"")</f>
+      <c r="S6">
+        <f>IFERROR(STDEV(M6:M7)/AVERAGE(M6:M7),"")</f>
         <v/>
       </c>
     </row>
@@ -2929,19 +2810,15 @@
         <f>IFERROR(J7/C7,"")</f>
         <v/>
       </c>
-      <c r="N7">
-        <f>IFERROR(M7/(0.7854*C7^2)*100,"")</f>
+      <c r="O7">
+        <f>IFERROR((M7-N7)/N7,"")</f>
         <v/>
       </c>
       <c r="P7">
-        <f>IFERROR((N7-O7)/O7,"")</f>
-        <v/>
-      </c>
-      <c r="Q7">
-        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(P7)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S7" t="inlineStr"/>
+        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2980,25 +2857,21 @@
         <f>IFERROR(J8/C8,"")</f>
         <v/>
       </c>
-      <c r="N8">
-        <f>IFERROR(M8/(0.7854*C8^2)*100,"")</f>
+      <c r="O8">
+        <f>IFERROR((M8-N8)/N8,"")</f>
         <v/>
       </c>
       <c r="P8">
-        <f>IFERROR((N8-O8)/O8,"")</f>
-        <v/>
-      </c>
-      <c r="Q8">
-        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(P8)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S8" t="inlineStr">
+        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>kV55.5×N58</t>
         </is>
       </c>
-      <c r="T8">
-        <f>IFERROR(STDEV(N8:N9)/AVERAGE(N8:N9),"")</f>
+      <c r="S8">
+        <f>IFERROR(STDEV(M8:M9)/AVERAGE(M8:M9),"")</f>
         <v/>
       </c>
     </row>
@@ -3039,19 +2912,15 @@
         <f>IFERROR(J9/C9,"")</f>
         <v/>
       </c>
-      <c r="N9">
-        <f>IFERROR(M9/(0.7854*C9^2)*100,"")</f>
+      <c r="O9">
+        <f>IFERROR((M9-N9)/N9,"")</f>
         <v/>
       </c>
       <c r="P9">
-        <f>IFERROR((N9-O9)/O9,"")</f>
-        <v/>
-      </c>
-      <c r="Q9">
-        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(P9)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S9" t="inlineStr"/>
+        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3090,25 +2959,21 @@
         <f>IFERROR(J10/C10,"")</f>
         <v/>
       </c>
-      <c r="N10">
-        <f>IFERROR(M10/(0.7854*C10^2)*100,"")</f>
+      <c r="O10">
+        <f>IFERROR((M10-N10)/N10,"")</f>
         <v/>
       </c>
       <c r="P10">
-        <f>IFERROR((N10-O10)/O10,"")</f>
-        <v/>
-      </c>
-      <c r="Q10">
-        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(P10)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S10" t="inlineStr">
+        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>kV59.5×N14</t>
         </is>
       </c>
-      <c r="T10">
-        <f>IFERROR(STDEV(N10:N11)/AVERAGE(N10:N11),"")</f>
+      <c r="S10">
+        <f>IFERROR(STDEV(M10:M11)/AVERAGE(M10:M11),"")</f>
         <v/>
       </c>
     </row>
@@ -3149,19 +3014,15 @@
         <f>IFERROR(J11/C11,"")</f>
         <v/>
       </c>
-      <c r="N11">
-        <f>IFERROR(M11/(0.7854*C11^2)*100,"")</f>
+      <c r="O11">
+        <f>IFERROR((M11-N11)/N11,"")</f>
         <v/>
       </c>
       <c r="P11">
-        <f>IFERROR((N11-O11)/O11,"")</f>
-        <v/>
-      </c>
-      <c r="Q11">
-        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(P11)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S11" t="inlineStr"/>
+        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3200,25 +3061,21 @@
         <f>IFERROR(J12/C12,"")</f>
         <v/>
       </c>
-      <c r="N12">
-        <f>IFERROR(M12/(0.7854*C12^2)*100,"")</f>
+      <c r="O12">
+        <f>IFERROR((M12-N12)/N12,"")</f>
         <v/>
       </c>
       <c r="P12">
-        <f>IFERROR((N12-O12)/O12,"")</f>
-        <v/>
-      </c>
-      <c r="Q12">
-        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(P12)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S12" t="inlineStr">
+        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(O12)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>kV59.5×N58</t>
         </is>
       </c>
-      <c r="T12">
-        <f>IFERROR(STDEV(N12:N13)/AVERAGE(N12:N13),"")</f>
+      <c r="S12">
+        <f>IFERROR(STDEV(M12:M13)/AVERAGE(M12:M13),"")</f>
         <v/>
       </c>
     </row>
@@ -3259,19 +3116,15 @@
         <f>IFERROR(J13/C13,"")</f>
         <v/>
       </c>
-      <c r="N13">
-        <f>IFERROR(M13/(0.7854*C13^2)*100,"")</f>
+      <c r="O13">
+        <f>IFERROR((M13-N13)/N13,"")</f>
         <v/>
       </c>
       <c r="P13">
-        <f>IFERROR((N13-O13)/O13,"")</f>
-        <v/>
-      </c>
-      <c r="Q13">
-        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(P13)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S13" t="inlineStr"/>
+        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(O13)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3310,25 +3163,21 @@
         <f>IFERROR(J14/C14,"")</f>
         <v/>
       </c>
-      <c r="N14">
-        <f>IFERROR(M14/(0.7854*C14^2)*100,"")</f>
+      <c r="O14">
+        <f>IFERROR((M14-N14)/N14,"")</f>
         <v/>
       </c>
       <c r="P14">
-        <f>IFERROR((N14-O14)/O14,"")</f>
-        <v/>
-      </c>
-      <c r="Q14">
-        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(P14)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S14" t="inlineStr">
+        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(O14)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>W4×F16</t>
         </is>
       </c>
-      <c r="T14">
-        <f>IFERROR(STDEV(N14:N15)/AVERAGE(N14:N15),"")</f>
+      <c r="S14">
+        <f>IFERROR(STDEV(M14:M15)/AVERAGE(M14:M15),"")</f>
         <v/>
       </c>
     </row>
@@ -3369,19 +3218,15 @@
         <f>IFERROR(J15/C15,"")</f>
         <v/>
       </c>
-      <c r="N15">
-        <f>IFERROR(M15/(0.7854*C15^2)*100,"")</f>
+      <c r="O15">
+        <f>IFERROR((M15-N15)/N15,"")</f>
         <v/>
       </c>
       <c r="P15">
-        <f>IFERROR((N15-O15)/O15,"")</f>
-        <v/>
-      </c>
-      <c r="Q15">
-        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(P15)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S15" t="inlineStr"/>
+        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(O15)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3420,25 +3265,21 @@
         <f>IFERROR(J16/C16,"")</f>
         <v/>
       </c>
-      <c r="N16">
-        <f>IFERROR(M16/(0.7854*C16^2)*100,"")</f>
+      <c r="O16">
+        <f>IFERROR((M16-N16)/N16,"")</f>
         <v/>
       </c>
       <c r="P16">
-        <f>IFERROR((N16-O16)/O16,"")</f>
-        <v/>
-      </c>
-      <c r="Q16">
-        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(P16)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S16" t="inlineStr">
+        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(O16)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R16" t="inlineStr">
         <is>
           <t>W4×F32</t>
         </is>
       </c>
-      <c r="T16">
-        <f>IFERROR(STDEV(N16:N17)/AVERAGE(N16:N17),"")</f>
+      <c r="S16">
+        <f>IFERROR(STDEV(M16:M17)/AVERAGE(M16:M17),"")</f>
         <v/>
       </c>
     </row>
@@ -3479,19 +3320,15 @@
         <f>IFERROR(J17/C17,"")</f>
         <v/>
       </c>
-      <c r="N17">
-        <f>IFERROR(M17/(0.7854*C17^2)*100,"")</f>
+      <c r="O17">
+        <f>IFERROR((M17-N17)/N17,"")</f>
         <v/>
       </c>
       <c r="P17">
-        <f>IFERROR((N17-O17)/O17,"")</f>
-        <v/>
-      </c>
-      <c r="Q17">
-        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(P17)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S17" t="inlineStr"/>
+        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(O17)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3530,25 +3367,21 @@
         <f>IFERROR(J18/C18,"")</f>
         <v/>
       </c>
-      <c r="N18">
-        <f>IFERROR(M18/(0.7854*C18^2)*100,"")</f>
+      <c r="O18">
+        <f>IFERROR((M18-N18)/N18,"")</f>
         <v/>
       </c>
       <c r="P18">
-        <f>IFERROR((N18-O18)/O18,"")</f>
-        <v/>
-      </c>
-      <c r="Q18">
-        <f>IF(J18="","",IF(AND(L18="Y",K18&gt;=0.97,K18&lt;=1.03,IFERROR(ABS(P18)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S18" t="inlineStr">
+        <f>IF(J18="","",IF(AND(L18="Y",K18&gt;=0.97,K18&lt;=1.03,IFERROR(ABS(O18)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R18" t="inlineStr">
         <is>
           <t>W6×F16</t>
         </is>
       </c>
-      <c r="T18">
-        <f>IFERROR(STDEV(N18:N19)/AVERAGE(N18:N19),"")</f>
+      <c r="S18">
+        <f>IFERROR(STDEV(M18:M19)/AVERAGE(M18:M19),"")</f>
         <v/>
       </c>
     </row>
@@ -3589,19 +3422,15 @@
         <f>IFERROR(J19/C19,"")</f>
         <v/>
       </c>
-      <c r="N19">
-        <f>IFERROR(M19/(0.7854*C19^2)*100,"")</f>
+      <c r="O19">
+        <f>IFERROR((M19-N19)/N19,"")</f>
         <v/>
       </c>
       <c r="P19">
-        <f>IFERROR((N19-O19)/O19,"")</f>
-        <v/>
-      </c>
-      <c r="Q19">
-        <f>IF(J19="","",IF(AND(L19="Y",K19&gt;=0.97,K19&lt;=1.03,IFERROR(ABS(P19)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S19" t="inlineStr"/>
+        <f>IF(J19="","",IF(AND(L19="Y",K19&gt;=0.97,K19&lt;=1.03,IFERROR(ABS(O19)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3640,25 +3469,21 @@
         <f>IFERROR(J20/C20,"")</f>
         <v/>
       </c>
-      <c r="N20">
-        <f>IFERROR(M20/(0.7854*C20^2)*100,"")</f>
+      <c r="O20">
+        <f>IFERROR((M20-N20)/N20,"")</f>
         <v/>
       </c>
       <c r="P20">
-        <f>IFERROR((N20-O20)/O20,"")</f>
-        <v/>
-      </c>
-      <c r="Q20">
-        <f>IF(J20="","",IF(AND(L20="Y",K20&gt;=0.97,K20&lt;=1.03,IFERROR(ABS(P20)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S20" t="inlineStr">
+        <f>IF(J20="","",IF(AND(L20="Y",K20&gt;=0.97,K20&lt;=1.03,IFERROR(ABS(O20)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R20" t="inlineStr">
         <is>
           <t>W6×F32</t>
         </is>
       </c>
-      <c r="T20">
-        <f>IFERROR(STDEV(N20:N21)/AVERAGE(N20:N21),"")</f>
+      <c r="S20">
+        <f>IFERROR(STDEV(M20:M21)/AVERAGE(M20:M21),"")</f>
         <v/>
       </c>
     </row>
@@ -3699,24 +3524,20 @@
         <f>IFERROR(J21/C21,"")</f>
         <v/>
       </c>
-      <c r="N21">
-        <f>IFERROR(M21/(0.7854*C21^2)*100,"")</f>
+      <c r="O21">
+        <f>IFERROR((M21-N21)/N21,"")</f>
         <v/>
       </c>
       <c r="P21">
-        <f>IFERROR((N21-O21)/O21,"")</f>
-        <v/>
-      </c>
-      <c r="Q21">
-        <f>IF(J21="","",IF(AND(L21="Y",K21&gt;=0.97,K21&lt;=1.03,IFERROR(ABS(P21)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S21" t="inlineStr"/>
+        <f>IF(J21="","",IF(AND(L21="Y",K21&gt;=0.97,K21&lt;=1.03,IFERROR(ABS(O21)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:S3"/>
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:R3"/>
+    <mergeCell ref="A2:R2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3728,7 +3549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3744,13 +3565,12 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3761,7 +3581,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>모델 산출 (kV,R,F,W)로 자재별 ×3반복. 합격: 매칭Y &amp; Q_dia 97~103% &amp; |void편차|≤10% &amp; σ≤3.5% &amp; tact 최소.</t>
         </is>
@@ -3770,7 +3590,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속). void%(N열)=PD면적 기준 자동.</t>
+          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비 출력(측정면적 기준) 그대로 입력.</t>
         </is>
       </c>
     </row>
@@ -3837,40 +3657,35 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>void면적(절대,µm²)</t>
+          <t>void%(측정,장비값)</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>void%(PD기준)(자동)</t>
+          <t>기준gold void%</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>기준gold void%(PD)</t>
+          <t>void편차%(자동)</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>void편차%(자동)</t>
+          <t>판정(자동)</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>판정(자동)</t>
+          <t>tact(초)</t>
         </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>tact(초)</t>
+          <t>메모</t>
         </is>
       </c>
       <c r="S5" s="6" t="inlineStr">
-        <is>
-          <t>메모</t>
-        </is>
-      </c>
-      <c r="T5" s="6" t="inlineStr">
         <is>
           <t>void%σ_rel(자동)</t>
         </is>
@@ -3919,25 +3734,21 @@
         <f>IFERROR(J6/C6,"")</f>
         <v/>
       </c>
-      <c r="N6">
-        <f>IFERROR(M6/(0.7854*C6^2)*100,"")</f>
+      <c r="O6">
+        <f>IFERROR((M6-N6)/N6,"")</f>
         <v/>
       </c>
       <c r="P6">
-        <f>IFERROR((N6-O6)/O6,"")</f>
-        <v/>
-      </c>
-      <c r="Q6">
-        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(P6)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S6" t="inlineStr">
+        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>모델 산출값 검증</t>
         </is>
       </c>
-      <c r="T6">
-        <f>IFERROR(STDEV(N6:N8)/AVERAGE(N6:N8),"")</f>
+      <c r="S6">
+        <f>IFERROR(STDEV(M6:M8)/AVERAGE(M6:M8),"")</f>
         <v/>
       </c>
     </row>
@@ -3984,19 +3795,15 @@
         <f>IFERROR(J7/C7,"")</f>
         <v/>
       </c>
-      <c r="N7">
-        <f>IFERROR(M7/(0.7854*C7^2)*100,"")</f>
+      <c r="O7">
+        <f>IFERROR((M7-N7)/N7,"")</f>
         <v/>
       </c>
       <c r="P7">
-        <f>IFERROR((N7-O7)/O7,"")</f>
-        <v/>
-      </c>
-      <c r="Q7">
-        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(P7)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S7" t="inlineStr"/>
+        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4041,19 +3848,15 @@
         <f>IFERROR(J8/C8,"")</f>
         <v/>
       </c>
-      <c r="N8">
-        <f>IFERROR(M8/(0.7854*C8^2)*100,"")</f>
+      <c r="O8">
+        <f>IFERROR((M8-N8)/N8,"")</f>
         <v/>
       </c>
       <c r="P8">
-        <f>IFERROR((N8-O8)/O8,"")</f>
-        <v/>
-      </c>
-      <c r="Q8">
-        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(P8)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S8" t="inlineStr"/>
+        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4098,25 +3901,21 @@
         <f>IFERROR(J9/C9,"")</f>
         <v/>
       </c>
-      <c r="N9">
-        <f>IFERROR(M9/(0.7854*C9^2)*100,"")</f>
+      <c r="O9">
+        <f>IFERROR((M9-N9)/N9,"")</f>
         <v/>
       </c>
       <c r="P9">
-        <f>IFERROR((N9-O9)/O9,"")</f>
-        <v/>
-      </c>
-      <c r="Q9">
-        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(P9)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S9" t="inlineStr">
+        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>모델 산출값 검증</t>
         </is>
       </c>
-      <c r="T9">
-        <f>IFERROR(STDEV(N9:N11)/AVERAGE(N9:N11),"")</f>
+      <c r="S9">
+        <f>IFERROR(STDEV(M9:M11)/AVERAGE(M9:M11),"")</f>
         <v/>
       </c>
     </row>
@@ -4163,19 +3962,15 @@
         <f>IFERROR(J10/C10,"")</f>
         <v/>
       </c>
-      <c r="N10">
-        <f>IFERROR(M10/(0.7854*C10^2)*100,"")</f>
+      <c r="O10">
+        <f>IFERROR((M10-N10)/N10,"")</f>
         <v/>
       </c>
       <c r="P10">
-        <f>IFERROR((N10-O10)/O10,"")</f>
-        <v/>
-      </c>
-      <c r="Q10">
-        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(P10)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S10" t="inlineStr"/>
+        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4220,24 +4015,20 @@
         <f>IFERROR(J11/C11,"")</f>
         <v/>
       </c>
-      <c r="N11">
-        <f>IFERROR(M11/(0.7854*C11^2)*100,"")</f>
+      <c r="O11">
+        <f>IFERROR((M11-N11)/N11,"")</f>
         <v/>
       </c>
       <c r="P11">
-        <f>IFERROR((N11-O11)/O11,"")</f>
-        <v/>
-      </c>
-      <c r="Q11">
-        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(P11)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="S11" t="inlineStr"/>
+        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:S3"/>
-    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:R3"/>
+    <mergeCell ref="A2:R2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4270,7 +4061,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>■ 확정할 계수(순전파)</t>
         </is>
@@ -4284,7 +4075,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>측정직경/PD=1+s·(kV−kV0). Phase1로 s·kV*(측정=PD 지점) 확정</t>
+          <t>측정직경/PD=1+s·(kV−kV0). Phase1로 s·kV*(측정=PD 지점)</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4099,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Phase2 F스윕: void%(PD) σ_rel≤3.5% 되는 최소 F</t>
+          <t>Phase2 F스윕: void% σ_rel≤3.5% 최소 F</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4123,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Phase3 kV×R·W×F 계수. 유의하면 항 추가</t>
+          <t>Phase3 kV×R·W×F 계수</t>
         </is>
       </c>
     </row>
@@ -4349,9 +4140,9 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>■ 역설계 규칙 (PD직경 D 입력 → 파라미터)</t>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>■ 역설계 규칙 (PD직경 D → 파라미터)</t>
         </is>
       </c>
     </row>
@@ -4387,7 +4178,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>R=D·√p/N_target (D=PD직경)</t>
+          <t>R=D·√p/N_target</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4221,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>※ 확정 계수는 레시피모델.xlsx·파라미터_계산기.xlsx 보정계수·N_target에 옮겨 적어 완성.</t>
+          <t>※ 확정 계수는 레시피모델.xlsx·파라미터_계산기.xlsx 보정계수·N_target에 옮겨 완성.</t>
         </is>
       </c>
     </row>

--- a/계산모델_엑셀/공정모델링_실험런시트_55런.xlsx
+++ b/계산모델_엑셀/공정모델링_실험런시트_55런.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PD로 확인한 실제 범프 직경. 자재 고유·고정(26·158µm). N 설계·자재 구분의 기준.</t>
+          <t>PD로 확인한 실제 범프 직경. 자재 고유·고정(26·158µm). N 설계·자재 구분 기준.</t>
         </is>
       </c>
     </row>
@@ -504,104 +504,122 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>■ void% 기준 = '측정 bump면적' (실제 .csv 확인)</t>
+          <t>■ void% 기준 = 측정 bump면적 (실제 .csv 확인)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>XRA_VOID.csv 검증: 각 범프 Area = π/4·(측정직경)² 로 정확히 일치(오차 0.00). 즉 장비는 void%를 'void면적 ÷ 측정 bump면적'으로 계산하고 8% 판정도 여기에 적용. → 이 런시트는 장비가 출력한 void%를 그대로 입력(M열). 측정직경이 kV로 변하면 분모(측정면적)도 함께 변하지만, 운영점은 측정직경=PD(Q_dia=100%)라 그 지점에선 측정면적=PD면적.</t>
+          <t>XRA_VOID.csv: 범프 Area = π/4·(측정직경)² 정확 일치 → void% = void면적÷측정면적, 8% 판정도 여기 적용. 런시트는 장비 출력 void%(M열) 그대로 입력. kV가 분모(측정면적)에도 작용해 void%에 이중효과.</t>
         </is>
       </c>
     </row>
     <row r="9"/>
     <row r="10"/>
-    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>■ 장비 제약: R 최소 = 0.2 µm/px  ★신규 반영</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>N = 0.283·PD직경 / R. R을 0.2 밑으로 못 내리므로 자재별 '가장 정밀한 N'에 상한이 생김: · 26µm → R0.2에서 N=37이 최대(픽셀오차 5.4%). 더 정밀 불가 → 26µm의 gold=R0.2(N37)이고 R로 속도 벌 여지 거의 없음(R은 0.2에 사실상 고정, 시간단축은 shot수·Frame으로). · 158µm → R0.2에서 N=223로 과잉 → R을 1.5(N30)까지 키워 속도 확보. R 자유도 큼. 결론: 작은 범프일수록 R 자유도가 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>■ 각 독립변수의 void 측정 메커니즘</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>대비 이동→경계 이동→void면적 변화(bias). 측정직경(=void% 분모)도 이동시켜 void%에 이중 작용.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>대비→경계 이동→void면적 bias. 측정직경(=분모)도 이동시켜 void%에 이중작용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>픽셀화 오차=2/N (N=0.283·PD직경/R). shot당 범프수·검사시간 ∝R².</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>픽셀화 오차=2/N. 단 R≥0.2 하한 → 26µm는 N≤37로 제한.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>두꺼운 범프 내부 광자부족→노이즈 void·경계 흔들림. 얇은 범프 둔감.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>랜덤 노이즈 평균화(∝1/√F)→반복 σ. 시간 정비례.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>랜덤 노이즈 평균화→반복 σ. 시간 정비례.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>■ 설계 원리</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>교호작용(kV×R,W×F,×D)→OFAT 불가. [주효과 스윕+의심 교호작용 2×2+같은범프 반복(σ)]. ε=10% 총예산 (2/N)²+(2σ)²≤10²→N_target≈29·σ≤3.5%. Ground truth 없어 자기참조(gold)+재현성 평가.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22"/>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>교호작용→OFAT 불가. [주효과 스윕+의심 교호작용 2×2+같은범프 반복(σ)]. ε=10% 총예산 (2/N)²+(2σ)²≤10² → N_target≈29(단 26µm은 R하한 탓에 N37 고정)·σ≤3.5%. Ground truth 없어 자기참조(gold)+재현성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27"/>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
+    <mergeCell ref="A8:H10"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="A8:H11"/>
-    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="A25:H27"/>
     <mergeCell ref="A7:H7"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="B21:H21"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A20:H22"/>
+    <mergeCell ref="B20:H20"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="B15:H15"/>
     <mergeCell ref="B5:H5"/>
+    <mergeCell ref="A13:H16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -646,14 +664,14 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>직경 다이얼(kV)·void 픽셀화(R) 스윕. R최소(N58)행=gold → 그 void%를 N열에. 고정 kV스윕:gold R·F32·W4 / R스윕:kV*·F32·W4</t>
+          <t>직경 다이얼(kV)·void 픽셀화(R). R최소행=gold → 그 void%를 N열에. 26µm gold=R0.2(N37,장비하한) / 158µm gold=R0.4(N112). 고정 F32·W4.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비 출력(측정면적 기준) 그대로 입력.</t>
+          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비 출력(측정면적 기준) / R≥0.2.</t>
         </is>
       </c>
     </row>
@@ -767,7 +785,7 @@
         <v>55.5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="F6">
         <f>IFERROR(ROUND(C6*0.2828/E6,0),"")</f>
@@ -818,7 +836,7 @@
         <v>57.5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="F7">
         <f>IFERROR(ROUND(C7*0.2828/E7,0),"")</f>
@@ -869,7 +887,7 @@
         <v>59.5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="F8">
         <f>IFERROR(ROUND(C8*0.2828/E8,0),"")</f>
@@ -920,7 +938,7 @@
         <v>58.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.77</v>
+        <v>0.4</v>
       </c>
       <c r="F9">
         <f>IFERROR(ROUND(C9*0.2828/E9,0),"")</f>
@@ -971,7 +989,7 @@
         <v>60.5</v>
       </c>
       <c r="E10" t="n">
-        <v>0.77</v>
+        <v>0.4</v>
       </c>
       <c r="F10">
         <f>IFERROR(ROUND(C10*0.2828/E10,0),"")</f>
@@ -1022,7 +1040,7 @@
         <v>62.5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.77</v>
+        <v>0.4</v>
       </c>
       <c r="F11">
         <f>IFERROR(ROUND(C11*0.2828/E11,0),"")</f>
@@ -1073,7 +1091,7 @@
         <v>57.5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="F12">
         <f>IFERROR(ROUND(C12*0.2828/E12,0),"")</f>
@@ -1102,7 +1120,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>N=58 =gold</t>
+          <t>N≈37 =gold(R하한)</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1142,7 @@
         <v>57.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="F13">
         <f>IFERROR(ROUND(C13*0.2828/E13,0),"")</f>
@@ -1153,7 +1171,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>N=29</t>
+          <t>N≈25</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1193,7 @@
         <v>57.5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="F14">
         <f>IFERROR(ROUND(C14*0.2828/E14,0),"")</f>
@@ -1204,7 +1222,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>N=14</t>
+          <t>N≈15</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1244,7 @@
         <v>60.5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.77</v>
+        <v>0.4</v>
       </c>
       <c r="F15">
         <f>IFERROR(ROUND(C15*0.2828/E15,0),"")</f>
@@ -1255,7 +1273,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>N=58 =gold</t>
+          <t>N≈112 =gold</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1295,7 @@
         <v>60.5</v>
       </c>
       <c r="E16" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F16">
         <f>IFERROR(ROUND(C16*0.2828/E16,0),"")</f>
@@ -1306,7 +1324,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>N=29</t>
+          <t>N≈30</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1346,7 @@
         <v>60.5</v>
       </c>
       <c r="E17" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="F17">
         <f>IFERROR(ROUND(C17*0.2828/E17,0),"")</f>
@@ -1357,7 +1375,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>N=14</t>
+          <t>N≈15</t>
         </is>
       </c>
     </row>
@@ -1410,14 +1428,14 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>같은 범프 반복→void% σ. 26µm=F스윕(W4), 158µm=W스윕(F32). 고정 kV*·R(N29).</t>
+          <t>같은 범프 반복→void% σ. 26µm=F스윕(R0.2·W4), 158µm=W스윕(R1.5·F32). kV*.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비 출력(측정면적 기준) 그대로 입력.</t>
+          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비 출력(측정면적 기준) / R≥0.2.</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1554,7 @@
         <v>57.5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F6">
         <f>IFERROR(ROUND(C6*0.2828/E6,0),"")</f>
@@ -1591,7 +1609,7 @@
         <v>57.5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F7">
         <f>IFERROR(ROUND(C7*0.2828/E7,0),"")</f>
@@ -1638,7 +1656,7 @@
         <v>57.5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F8">
         <f>IFERROR(ROUND(C8*0.2828/E8,0),"")</f>
@@ -1685,7 +1703,7 @@
         <v>57.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F9">
         <f>IFERROR(ROUND(C9*0.2828/E9,0),"")</f>
@@ -1740,7 +1758,7 @@
         <v>57.5</v>
       </c>
       <c r="E10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F10">
         <f>IFERROR(ROUND(C10*0.2828/E10,0),"")</f>
@@ -1787,7 +1805,7 @@
         <v>57.5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F11">
         <f>IFERROR(ROUND(C11*0.2828/E11,0),"")</f>
@@ -1834,7 +1852,7 @@
         <v>57.5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F12">
         <f>IFERROR(ROUND(C12*0.2828/E12,0),"")</f>
@@ -1889,7 +1907,7 @@
         <v>57.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F13">
         <f>IFERROR(ROUND(C13*0.2828/E13,0),"")</f>
@@ -1936,7 +1954,7 @@
         <v>57.5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F14">
         <f>IFERROR(ROUND(C14*0.2828/E14,0),"")</f>
@@ -1983,7 +2001,7 @@
         <v>60.5</v>
       </c>
       <c r="E15" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F15">
         <f>IFERROR(ROUND(C15*0.2828/E15,0),"")</f>
@@ -2038,7 +2056,7 @@
         <v>60.5</v>
       </c>
       <c r="E16" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F16">
         <f>IFERROR(ROUND(C16*0.2828/E16,0),"")</f>
@@ -2085,7 +2103,7 @@
         <v>60.5</v>
       </c>
       <c r="E17" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F17">
         <f>IFERROR(ROUND(C17*0.2828/E17,0),"")</f>
@@ -2132,7 +2150,7 @@
         <v>60.5</v>
       </c>
       <c r="E18" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F18">
         <f>IFERROR(ROUND(C18*0.2828/E18,0),"")</f>
@@ -2187,7 +2205,7 @@
         <v>60.5</v>
       </c>
       <c r="E19" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F19">
         <f>IFERROR(ROUND(C19*0.2828/E19,0),"")</f>
@@ -2234,7 +2252,7 @@
         <v>60.5</v>
       </c>
       <c r="E20" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F20">
         <f>IFERROR(ROUND(C20*0.2828/E20,0),"")</f>
@@ -2281,7 +2299,7 @@
         <v>60.5</v>
       </c>
       <c r="E21" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F21">
         <f>IFERROR(ROUND(C21*0.2828/E21,0),"")</f>
@@ -2336,7 +2354,7 @@
         <v>60.5</v>
       </c>
       <c r="E22" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F22">
         <f>IFERROR(ROUND(C22*0.2828/E22,0),"")</f>
@@ -2383,7 +2401,7 @@
         <v>60.5</v>
       </c>
       <c r="E23" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F23">
         <f>IFERROR(ROUND(C23*0.2828/E23,0),"")</f>
@@ -2430,7 +2448,7 @@
         <v>60.5</v>
       </c>
       <c r="E24" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F24">
         <f>IFERROR(ROUND(C24*0.2828/E24,0),"")</f>
@@ -2485,7 +2503,7 @@
         <v>60.5</v>
       </c>
       <c r="E25" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F25">
         <f>IFERROR(ROUND(C25*0.2828/E25,0),"")</f>
@@ -2532,7 +2550,7 @@
         <v>60.5</v>
       </c>
       <c r="E26" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F26">
         <f>IFERROR(ROUND(C26*0.2828/E26,0),"")</f>
@@ -2610,14 +2628,14 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>kV×R(26µm): 대비bias×픽셀화 / W×F(158µm): SNR∝√(W·F) 교환. ×D는 두 자재로 확인.</t>
+          <t>kV×R(26µm): 대비bias×픽셀화 / W×F(158µm): SNR∝√(W·F) 교환. ×D는 두 자재.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비 출력(측정면적 기준) 그대로 입력.</t>
+          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비 출력(측정면적 기준) / R≥0.2.</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2754,7 @@
         <v>55.5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.53</v>
+        <v>0.2</v>
       </c>
       <c r="F6">
         <f>IFERROR(ROUND(C6*0.2828/E6,0),"")</f>
@@ -2765,7 +2783,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>kV55.5×N14</t>
+          <t>kV55.5×R0.2(N37)</t>
         </is>
       </c>
       <c r="S6">
@@ -2791,7 +2809,7 @@
         <v>55.5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.53</v>
+        <v>0.2</v>
       </c>
       <c r="F7">
         <f>IFERROR(ROUND(C7*0.2828/E7,0),"")</f>
@@ -2838,7 +2856,7 @@
         <v>55.5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
       <c r="F8">
         <f>IFERROR(ROUND(C8*0.2828/E8,0),"")</f>
@@ -2867,7 +2885,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>kV55.5×N58</t>
+          <t>kV55.5×R0.5(N15)</t>
         </is>
       </c>
       <c r="S8">
@@ -2893,7 +2911,7 @@
         <v>55.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
       <c r="F9">
         <f>IFERROR(ROUND(C9*0.2828/E9,0),"")</f>
@@ -2940,7 +2958,7 @@
         <v>59.5</v>
       </c>
       <c r="E10" t="n">
-        <v>0.53</v>
+        <v>0.2</v>
       </c>
       <c r="F10">
         <f>IFERROR(ROUND(C10*0.2828/E10,0),"")</f>
@@ -2969,7 +2987,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>kV59.5×N14</t>
+          <t>kV59.5×R0.2(N37)</t>
         </is>
       </c>
       <c r="S10">
@@ -2995,7 +3013,7 @@
         <v>59.5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.53</v>
+        <v>0.2</v>
       </c>
       <c r="F11">
         <f>IFERROR(ROUND(C11*0.2828/E11,0),"")</f>
@@ -3042,7 +3060,7 @@
         <v>59.5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
       <c r="F12">
         <f>IFERROR(ROUND(C12*0.2828/E12,0),"")</f>
@@ -3071,7 +3089,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>kV59.5×N58</t>
+          <t>kV59.5×R0.5(N15)</t>
         </is>
       </c>
       <c r="S12">
@@ -3097,7 +3115,7 @@
         <v>59.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
       <c r="F13">
         <f>IFERROR(ROUND(C13*0.2828/E13,0),"")</f>
@@ -3144,7 +3162,7 @@
         <v>60.5</v>
       </c>
       <c r="E14" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F14">
         <f>IFERROR(ROUND(C14*0.2828/E14,0),"")</f>
@@ -3199,7 +3217,7 @@
         <v>60.5</v>
       </c>
       <c r="E15" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F15">
         <f>IFERROR(ROUND(C15*0.2828/E15,0),"")</f>
@@ -3246,7 +3264,7 @@
         <v>60.5</v>
       </c>
       <c r="E16" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F16">
         <f>IFERROR(ROUND(C16*0.2828/E16,0),"")</f>
@@ -3301,7 +3319,7 @@
         <v>60.5</v>
       </c>
       <c r="E17" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F17">
         <f>IFERROR(ROUND(C17*0.2828/E17,0),"")</f>
@@ -3348,7 +3366,7 @@
         <v>60.5</v>
       </c>
       <c r="E18" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F18">
         <f>IFERROR(ROUND(C18*0.2828/E18,0),"")</f>
@@ -3403,7 +3421,7 @@
         <v>60.5</v>
       </c>
       <c r="E19" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F19">
         <f>IFERROR(ROUND(C19*0.2828/E19,0),"")</f>
@@ -3450,7 +3468,7 @@
         <v>60.5</v>
       </c>
       <c r="E20" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F20">
         <f>IFERROR(ROUND(C20*0.2828/E20,0),"")</f>
@@ -3505,7 +3523,7 @@
         <v>60.5</v>
       </c>
       <c r="E21" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="F21">
         <f>IFERROR(ROUND(C21*0.2828/E21,0),"")</f>
@@ -3583,14 +3601,14 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>모델 산출 (kV,R,F,W)로 자재별 ×3반복. 합격: 매칭Y &amp; Q_dia 97~103% &amp; |void편차|≤10% &amp; σ≤3.5% &amp; tact 최소.</t>
+          <t>모델 산출 (kV,R,F,W)로 자재별 ×3반복. 합격: 매칭Y &amp; Q_dia97~103% &amp; |void편차|≤10% &amp; σ≤3.5% &amp; tact 최소.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비 출력(측정면적 기준) 그대로 입력.</t>
+          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비 출력(측정면적 기준) / R≥0.2.</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3730,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(모델R)</t>
+          <t>(모델R≥0.2)</t>
         </is>
       </c>
       <c r="F6">
@@ -3773,7 +3791,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(모델R)</t>
+          <t>(모델R≥0.2)</t>
         </is>
       </c>
       <c r="F7">
@@ -3826,7 +3844,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(모델R)</t>
+          <t>(모델R≥0.2)</t>
         </is>
       </c>
       <c r="F8">
@@ -4063,7 +4081,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>■ 확정할 계수(순전파)</t>
+          <t>■ 확정할 계수</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4093,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>측정직경/PD=1+s·(kV−kV0). Phase1로 s·kV*(측정=PD 지점)</t>
+          <t>측정직경/PD=1+s·(kV−kV0). Phase1로 s·kV*</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4105,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Phase1 R스윕: gold 대비 |void편차| 7% 넘는 N. 이론≈29</t>
+          <t>Phase1 R스윕: gold 대비 |void편차| 7% 넘는 N(≈29). 단 26µm은 R하한으로 N37 고정→R0.2</t>
         </is>
       </c>
     </row>
@@ -4130,12 +4148,12 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>tact(R,F)</t>
+          <t>tact</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>tact=a·(shot수·F)+b, shot수=ROUNDUP(목표범프/(R²비례))</t>
+          <t>tact=a·(shot수·F)+b. 26µm은 R고정→shot수·F로만 단축</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4184,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>kV*(D) 직선서 읽고 1kV씩 트림해 측정직경=PD(100%)</t>
+          <t>kV*(D)서 시작해 1kV씩 트림→측정직경=PD(100%)</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4196,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>R=D·√p/N_target</t>
+          <t>R=max(0.2, D·√p/N_target). 작은 범프는 0.2에 걸림</t>
         </is>
       </c>
     </row>

--- a/계산모델_엑셀/공정모델링_실험런시트_55런.xlsx
+++ b/계산모델_엑셀/공정모델링_실험런시트_55런.xlsx
@@ -520,14 +520,14 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ 장비 제약: R 최소 = 0.2 µm/px  ★신규 반영</t>
+          <t>■ R–N–범프크기 관계 (중요)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>N = 0.283·PD직경 / R. R을 0.2 밑으로 못 내리므로 자재별 '가장 정밀한 N'에 상한이 생김: · 26µm → R0.2에서 N=37이 최대(픽셀오차 5.4%). 더 정밀 불가 → 26µm의 gold=R0.2(N37)이고 R로 속도 벌 여지 거의 없음(R은 0.2에 사실상 고정, 시간단축은 shot수·Frame으로). · 158µm → R0.2에서 N=223로 과잉 → R을 1.5(N30)까지 키워 속도 확보. R 자유도 큼. 결론: 작은 범프일수록 R 자유도가 없다.</t>
+          <t>N = 0.283·PD직경 / R (N=void가 담기는 픽셀 수). 같은 N을 얻는 R = 0.283·D/N → 범프가 클수록 R을 높여도 됨. 'N 클수록 검출 유리'는 맞지만 N_target(~29) 넘으면 판정 오차는 이미 예산 안이라 그 이상은 시간낭비(시간∝1/R²). 따라서 최적 R = N_target을 주는 '가장 높은(거친) R'. 큰 범프일수록 이 값이 높다.</t>
         </is>
       </c>
     </row>
@@ -535,60 +535,22 @@
     <row r="15"/>
     <row r="16"/>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>■ 각 독립변수의 void 측정 메커니즘</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>■ 장비 제약 R≥0.2 + 자재별 R (운영값)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>kV</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>대비→경계 이동→void면적 bias. 측정직경(=분모)도 이동시켜 void%에 이중작용.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>픽셀화 오차=2/N. 단 R≥0.2 하한 → 26µm는 N≤37로 제한.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>두꺼운 범프 내부 광자부족→노이즈 void·경계 흔들림. 얇은 범프 둔감.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>랜덤 노이즈 평균화→반복 σ. 시간 정비례.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>· 26µm: R0.2에서 N=37이 최대(픽셀오차5.4%). R 자유도 거의 없음(0.2 고정) → 시간단축은 shot수·Frame. · 158µm: 운영 R=1.5(N30)로 높음. R스윕 최저점 gold(R0.77·N58)은 '기준 truth'용 앵커일 뿐 운영값 아님 (큰 범프는 R 높여도 N 충분). → 작은 범프일수록 R 자유도가 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
@@ -599,24 +561,22 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>교호작용→OFAT 불가. [주효과 스윕+의심 교호작용 2×2+같은범프 반복(σ)]. ε=10% 총예산 (2/N)²+(2σ)²≤10² → N_target≈29(단 26µm은 R하한 탓에 N37 고정)·σ≤3.5%. Ground truth 없어 자기참조(gold)+재현성.</t>
+          <t>교호작용→OFAT 불가. [주효과 스윕+의심 교호작용 2×2+같은범프 반복(σ)]. ε=10% 총예산 (2/N)²+(2σ)²≤10² → N_target≈29(26µm은 R하한 탓 N37)·σ≤3.5%. Ground truth 없어 자기참조(gold)+재현성.</t>
         </is>
       </c>
     </row>
     <row r="26"/>
     <row r="27"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="11">
     <mergeCell ref="A8:H10"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A25:H27"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="A19:H22"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B20:H20"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B5:H5"/>
     <mergeCell ref="A13:H16"/>
@@ -664,14 +624,14 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>직경 다이얼(kV)·void 픽셀화(R). R최소행=gold → 그 void%를 N열에. 26µm gold=R0.2(N37,장비하한) / 158µm gold=R0.4(N112). 고정 F32·W4.</t>
+          <t>직경 다이얼(kV)·void 픽셀화(R). gold(최정밀행)=기준 truth 앵커. 26µm gold=R0.2(N37,장비하한) / 158µm gold=R0.77(N58). 고정 F32·W4.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비 출력(측정면적 기준) / R≥0.2.</t>
+          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / R≥0.2 · 큰 범프일수록 R↑.</t>
         </is>
       </c>
     </row>
@@ -938,7 +898,7 @@
         <v>58.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4</v>
+        <v>0.77</v>
       </c>
       <c r="F9">
         <f>IFERROR(ROUND(C9*0.2828/E9,0),"")</f>
@@ -989,7 +949,7 @@
         <v>60.5</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4</v>
+        <v>0.77</v>
       </c>
       <c r="F10">
         <f>IFERROR(ROUND(C10*0.2828/E10,0),"")</f>
@@ -1040,7 +1000,7 @@
         <v>62.5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4</v>
+        <v>0.77</v>
       </c>
       <c r="F11">
         <f>IFERROR(ROUND(C11*0.2828/E11,0),"")</f>
@@ -1244,7 +1204,7 @@
         <v>60.5</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4</v>
+        <v>0.77</v>
       </c>
       <c r="F15">
         <f>IFERROR(ROUND(C15*0.2828/E15,0),"")</f>
@@ -1273,7 +1233,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>N≈112 =gold</t>
+          <t>N≈58 =gold(기준앵커)</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1395,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비 출력(측정면적 기준) / R≥0.2.</t>
+          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / R≥0.2 · 큰 범프일수록 R↑.</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2595,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비 출력(측정면적 기준) / R≥0.2.</t>
+          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / R≥0.2 · 큰 범프일수록 R↑.</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3568,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비 출력(측정면적 기준) / R≥0.2.</t>
+          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / R≥0.2 · 큰 범프일수록 R↑.</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3857,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(모델R)</t>
+          <t>(모델R,높음)</t>
         </is>
       </c>
       <c r="F9">
@@ -3958,7 +3918,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(모델R)</t>
+          <t>(모델R,높음)</t>
         </is>
       </c>
       <c r="F10">
@@ -4011,7 +3971,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(모델R)</t>
+          <t>(모델R,높음)</t>
         </is>
       </c>
       <c r="F11">
@@ -4105,7 +4065,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Phase1 R스윕: gold 대비 |void편차| 7% 넘는 N(≈29). 단 26µm은 R하한으로 N37 고정→R0.2</t>
+          <t>Phase1 R스윕: gold 대비 |void편차| 7% 넘는 N(≈29). 26µm은 R하한→N37 고정(R0.2)</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4156,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>R=max(0.2, D·√p/N_target). 작은 범프는 0.2에 걸림</t>
+          <t>R = max(0.2, D·√p/N_target). 큰 범프일수록 R↑ / 작은 범프는 0.2에 걸림</t>
         </is>
       </c>
     </row>

--- a/계산모델_엑셀/공정모델링_실험런시트_55런.xlsx
+++ b/계산모델_엑셀/공정모델링_실험런시트_55런.xlsx
@@ -64,7 +64,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -77,6 +77,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -567,15 +570,35 @@
     </row>
     <row r="26"/>
     <row r="27"/>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>■ 26µm 측정오차 목표: 10%→13%로 완화 (R하한 반영, 잠정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>R=0.2에서 N=37 → 픽셀화오차 2/N=5.4%가 고정(더 못 내림, R 하한). 총오차=√(5.4²+(2σ)²). 노이즈 2σ~12%(σ~6%, 보통 Frame)면 총 ≈13%. → 26µm은 ε=13%(잠정) 권장, 158µm 등은 10% 유지. 10% 고집 시 σ≤4.2% 강요→Frame·시간 낭비(검사시간 최소화와 충돌). 물리 하한 ~6%(노이즈0)라 5% 이하 불가. 게이지 '허용' 범위 내. 최종값은 Phase2 실측 σ로 √(5.4²+(2σ)²) 확정(노이즈 낮으면 10%로 재조임). 판정 수식도 26µm=±13%, 그 외=±10% 로 반영함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
     <mergeCell ref="A8:H10"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A30:H34"/>
     <mergeCell ref="A25:H27"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A19:H22"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="B6:H6"/>
     <mergeCell ref="B5:H5"/>
@@ -769,7 +792,7 @@
         <v/>
       </c>
       <c r="P6">
-        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=IF(B6="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R6" t="inlineStr">
@@ -820,7 +843,7 @@
         <v/>
       </c>
       <c r="P7">
-        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=IF(B7="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R7" t="inlineStr">
@@ -871,7 +894,7 @@
         <v/>
       </c>
       <c r="P8">
-        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=IF(B8="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R8" t="inlineStr">
@@ -922,7 +945,7 @@
         <v/>
       </c>
       <c r="P9">
-        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=IF(B9="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R9" t="inlineStr">
@@ -973,7 +996,7 @@
         <v/>
       </c>
       <c r="P10">
-        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=IF(B10="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R10" t="inlineStr">
@@ -1024,7 +1047,7 @@
         <v/>
       </c>
       <c r="P11">
-        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=IF(B11="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R11" t="inlineStr">
@@ -1075,7 +1098,7 @@
         <v/>
       </c>
       <c r="P12">
-        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(O12)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(O12)&lt;=IF(B12="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R12" t="inlineStr">
@@ -1126,7 +1149,7 @@
         <v/>
       </c>
       <c r="P13">
-        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(O13)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(O13)&lt;=IF(B13="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R13" t="inlineStr">
@@ -1177,7 +1200,7 @@
         <v/>
       </c>
       <c r="P14">
-        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(O14)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(O14)&lt;=IF(B14="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R14" t="inlineStr">
@@ -1228,7 +1251,7 @@
         <v/>
       </c>
       <c r="P15">
-        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(O15)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(O15)&lt;=IF(B15="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R15" t="inlineStr">
@@ -1279,7 +1302,7 @@
         <v/>
       </c>
       <c r="P16">
-        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(O16)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(O16)&lt;=IF(B16="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R16" t="inlineStr">
@@ -1330,7 +1353,7 @@
         <v/>
       </c>
       <c r="P17">
-        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(O17)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(O17)&lt;=IF(B17="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R17" t="inlineStr">
@@ -1538,7 +1561,7 @@
         <v/>
       </c>
       <c r="P6">
-        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=IF(B6="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R6" t="inlineStr">
@@ -1593,10 +1616,9 @@
         <v/>
       </c>
       <c r="P7">
-        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R7" t="inlineStr"/>
+        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=IF(B7="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1640,10 +1662,9 @@
         <v/>
       </c>
       <c r="P8">
-        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R8" t="inlineStr"/>
+        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=IF(B8="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1687,7 +1708,7 @@
         <v/>
       </c>
       <c r="P9">
-        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=IF(B9="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R9" t="inlineStr">
@@ -1742,10 +1763,9 @@
         <v/>
       </c>
       <c r="P10">
-        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R10" t="inlineStr"/>
+        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=IF(B10="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1789,10 +1809,9 @@
         <v/>
       </c>
       <c r="P11">
-        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R11" t="inlineStr"/>
+        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=IF(B11="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1836,7 +1855,7 @@
         <v/>
       </c>
       <c r="P12">
-        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(O12)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(O12)&lt;=IF(B12="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R12" t="inlineStr">
@@ -1891,10 +1910,9 @@
         <v/>
       </c>
       <c r="P13">
-        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(O13)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R13" t="inlineStr"/>
+        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(O13)&lt;=IF(B13="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1938,10 +1956,9 @@
         <v/>
       </c>
       <c r="P14">
-        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(O14)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R14" t="inlineStr"/>
+        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(O14)&lt;=IF(B14="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1985,7 +2002,7 @@
         <v/>
       </c>
       <c r="P15">
-        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(O15)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(O15)&lt;=IF(B15="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R15" t="inlineStr">
@@ -2040,10 +2057,9 @@
         <v/>
       </c>
       <c r="P16">
-        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(O16)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R16" t="inlineStr"/>
+        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(O16)&lt;=IF(B16="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2087,10 +2103,9 @@
         <v/>
       </c>
       <c r="P17">
-        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(O17)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R17" t="inlineStr"/>
+        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(O17)&lt;=IF(B17="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2134,7 +2149,7 @@
         <v/>
       </c>
       <c r="P18">
-        <f>IF(J18="","",IF(AND(L18="Y",K18&gt;=0.97,K18&lt;=1.03,IFERROR(ABS(O18)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J18="","",IF(AND(L18="Y",K18&gt;=0.97,K18&lt;=1.03,IFERROR(ABS(O18)&lt;=IF(B18="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R18" t="inlineStr">
@@ -2189,10 +2204,9 @@
         <v/>
       </c>
       <c r="P19">
-        <f>IF(J19="","",IF(AND(L19="Y",K19&gt;=0.97,K19&lt;=1.03,IFERROR(ABS(O19)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R19" t="inlineStr"/>
+        <f>IF(J19="","",IF(AND(L19="Y",K19&gt;=0.97,K19&lt;=1.03,IFERROR(ABS(O19)&lt;=IF(B19="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2236,10 +2250,9 @@
         <v/>
       </c>
       <c r="P20">
-        <f>IF(J20="","",IF(AND(L20="Y",K20&gt;=0.97,K20&lt;=1.03,IFERROR(ABS(O20)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R20" t="inlineStr"/>
+        <f>IF(J20="","",IF(AND(L20="Y",K20&gt;=0.97,K20&lt;=1.03,IFERROR(ABS(O20)&lt;=IF(B20="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2283,7 +2296,7 @@
         <v/>
       </c>
       <c r="P21">
-        <f>IF(J21="","",IF(AND(L21="Y",K21&gt;=0.97,K21&lt;=1.03,IFERROR(ABS(O21)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J21="","",IF(AND(L21="Y",K21&gt;=0.97,K21&lt;=1.03,IFERROR(ABS(O21)&lt;=IF(B21="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R21" t="inlineStr">
@@ -2338,10 +2351,9 @@
         <v/>
       </c>
       <c r="P22">
-        <f>IF(J22="","",IF(AND(L22="Y",K22&gt;=0.97,K22&lt;=1.03,IFERROR(ABS(O22)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R22" t="inlineStr"/>
+        <f>IF(J22="","",IF(AND(L22="Y",K22&gt;=0.97,K22&lt;=1.03,IFERROR(ABS(O22)&lt;=IF(B22="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2385,10 +2397,9 @@
         <v/>
       </c>
       <c r="P23">
-        <f>IF(J23="","",IF(AND(L23="Y",K23&gt;=0.97,K23&lt;=1.03,IFERROR(ABS(O23)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R23" t="inlineStr"/>
+        <f>IF(J23="","",IF(AND(L23="Y",K23&gt;=0.97,K23&lt;=1.03,IFERROR(ABS(O23)&lt;=IF(B23="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2432,7 +2443,7 @@
         <v/>
       </c>
       <c r="P24">
-        <f>IF(J24="","",IF(AND(L24="Y",K24&gt;=0.97,K24&lt;=1.03,IFERROR(ABS(O24)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J24="","",IF(AND(L24="Y",K24&gt;=0.97,K24&lt;=1.03,IFERROR(ABS(O24)&lt;=IF(B24="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R24" t="inlineStr">
@@ -2487,10 +2498,9 @@
         <v/>
       </c>
       <c r="P25">
-        <f>IF(J25="","",IF(AND(L25="Y",K25&gt;=0.97,K25&lt;=1.03,IFERROR(ABS(O25)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R25" t="inlineStr"/>
+        <f>IF(J25="","",IF(AND(L25="Y",K25&gt;=0.97,K25&lt;=1.03,IFERROR(ABS(O25)&lt;=IF(B25="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2534,10 +2544,9 @@
         <v/>
       </c>
       <c r="P26">
-        <f>IF(J26="","",IF(AND(L26="Y",K26&gt;=0.97,K26&lt;=1.03,IFERROR(ABS(O26)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R26" t="inlineStr"/>
+        <f>IF(J26="","",IF(AND(L26="Y",K26&gt;=0.97,K26&lt;=1.03,IFERROR(ABS(O26)&lt;=IF(B26="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2738,7 +2747,7 @@
         <v/>
       </c>
       <c r="P6">
-        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=IF(B6="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R6" t="inlineStr">
@@ -2793,10 +2802,9 @@
         <v/>
       </c>
       <c r="P7">
-        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R7" t="inlineStr"/>
+        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=IF(B7="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2840,7 +2848,7 @@
         <v/>
       </c>
       <c r="P8">
-        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=IF(B8="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R8" t="inlineStr">
@@ -2895,10 +2903,9 @@
         <v/>
       </c>
       <c r="P9">
-        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R9" t="inlineStr"/>
+        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=IF(B9="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2942,7 +2949,7 @@
         <v/>
       </c>
       <c r="P10">
-        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=IF(B10="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R10" t="inlineStr">
@@ -2997,10 +3004,9 @@
         <v/>
       </c>
       <c r="P11">
-        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R11" t="inlineStr"/>
+        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=IF(B11="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3044,7 +3050,7 @@
         <v/>
       </c>
       <c r="P12">
-        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(O12)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(O12)&lt;=IF(B12="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R12" t="inlineStr">
@@ -3099,10 +3105,9 @@
         <v/>
       </c>
       <c r="P13">
-        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(O13)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R13" t="inlineStr"/>
+        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(O13)&lt;=IF(B13="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3146,7 +3151,7 @@
         <v/>
       </c>
       <c r="P14">
-        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(O14)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(O14)&lt;=IF(B14="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R14" t="inlineStr">
@@ -3201,10 +3206,9 @@
         <v/>
       </c>
       <c r="P15">
-        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(O15)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R15" t="inlineStr"/>
+        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(O15)&lt;=IF(B15="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3248,7 +3252,7 @@
         <v/>
       </c>
       <c r="P16">
-        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(O16)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(O16)&lt;=IF(B16="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R16" t="inlineStr">
@@ -3303,10 +3307,9 @@
         <v/>
       </c>
       <c r="P17">
-        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(O17)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R17" t="inlineStr"/>
+        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(O17)&lt;=IF(B17="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3350,7 +3353,7 @@
         <v/>
       </c>
       <c r="P18">
-        <f>IF(J18="","",IF(AND(L18="Y",K18&gt;=0.97,K18&lt;=1.03,IFERROR(ABS(O18)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J18="","",IF(AND(L18="Y",K18&gt;=0.97,K18&lt;=1.03,IFERROR(ABS(O18)&lt;=IF(B18="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R18" t="inlineStr">
@@ -3405,10 +3408,9 @@
         <v/>
       </c>
       <c r="P19">
-        <f>IF(J19="","",IF(AND(L19="Y",K19&gt;=0.97,K19&lt;=1.03,IFERROR(ABS(O19)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R19" t="inlineStr"/>
+        <f>IF(J19="","",IF(AND(L19="Y",K19&gt;=0.97,K19&lt;=1.03,IFERROR(ABS(O19)&lt;=IF(B19="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3452,7 +3454,7 @@
         <v/>
       </c>
       <c r="P20">
-        <f>IF(J20="","",IF(AND(L20="Y",K20&gt;=0.97,K20&lt;=1.03,IFERROR(ABS(O20)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J20="","",IF(AND(L20="Y",K20&gt;=0.97,K20&lt;=1.03,IFERROR(ABS(O20)&lt;=IF(B20="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R20" t="inlineStr">
@@ -3507,10 +3509,9 @@
         <v/>
       </c>
       <c r="P21">
-        <f>IF(J21="","",IF(AND(L21="Y",K21&gt;=0.97,K21&lt;=1.03,IFERROR(ABS(O21)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R21" t="inlineStr"/>
+        <f>IF(J21="","",IF(AND(L21="Y",K21&gt;=0.97,K21&lt;=1.03,IFERROR(ABS(O21)&lt;=IF(B21="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3717,7 +3718,7 @@
         <v/>
       </c>
       <c r="P6">
-        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=IF(B6="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R6" t="inlineStr">
@@ -3778,10 +3779,9 @@
         <v/>
       </c>
       <c r="P7">
-        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R7" t="inlineStr"/>
+        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=IF(B7="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3831,10 +3831,9 @@
         <v/>
       </c>
       <c r="P8">
-        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R8" t="inlineStr"/>
+        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=IF(B8="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3884,7 +3883,7 @@
         <v/>
       </c>
       <c r="P9">
-        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=IF(B9="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R9" t="inlineStr">
@@ -3945,10 +3944,9 @@
         <v/>
       </c>
       <c r="P10">
-        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R10" t="inlineStr"/>
+        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=IF(B10="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3998,10 +3996,9 @@
         <v/>
       </c>
       <c r="P11">
-        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
-      <c r="R11" t="inlineStr"/>
+        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=IF(B11="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/계산모델_엑셀/공정모델링_실험런시트_55런.xlsx
+++ b/계산모델_엑셀/공정모델링_실험런시트_55런.xlsx
@@ -64,7 +64,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -77,9 +77,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -446,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -514,7 +511,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>XRA_VOID.csv: 범프 Area = π/4·(측정직경)² 정확 일치 → void% = void면적÷측정면적, 8% 판정도 여기 적용. 런시트는 장비 출력 void%(M열) 그대로 입력. kV가 분모(측정면적)에도 작용해 void%에 이중효과.</t>
+          <t>XRA_VOID.csv: 범프 Area = π/4·(측정직경)² 정확 일치 → void% = void면적÷측정면적, 8% 판정도 여기 적용. 런시트는 장비 출력 void%(M열) 그대로 입력. 이 관계는 측정직경=PD(Q_dia=100%)일 때만 성립 → 그래서 kV를 먼저 맞춤.</t>
         </is>
       </c>
     </row>
@@ -523,86 +520,63 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ R–N–범프크기 관계 (중요)</t>
+          <t>■ 측정오차 ε=10% = '픽셀화(해상도)만' → N=2/ε=20 (전 자재 통일) ★</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>N = 0.283·PD직경 / R (N=void가 담기는 픽셀 수). 같은 N을 얻는 R = 0.283·D/N → 범프가 클수록 R을 높여도 됨. 'N 클수록 검출 유리'는 맞지만 N_target(~29) 넘으면 판정 오차는 이미 예산 안이라 그 이상은 시간낭비(시간∝1/R²). 따라서 최적 R = N_target을 주는 '가장 높은(거친) R'. 큰 범프일수록 이 값이 높다.</t>
+          <t>void 면적 픽셀화오차 ≈ 2/N. ε=10%로 두면 N=20. 노이즈는 이 10%에 미포함 — Frame으로 σ 별도 관리(정밀도 축 분리). 파라미터_계산기·레시피모델(N_target=20)과 동일 기준. R = √p·D/20 = 0.0141·D → 큰 범프일수록 R↑.</t>
         </is>
       </c>
     </row>
     <row r="14"/>
     <row r="15"/>
-    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>■ 자재별 R (운영값, N=20)</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>■ 장비 제약 R≥0.2 + 자재별 R (운영값)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>· 26µm: R0.2에서 N=37이 최대(픽셀오차5.4%). R 자유도 거의 없음(0.2 고정) → 시간단축은 shot수·Frame. · 158µm: 운영 R=1.5(N30)로 높음. R스윕 최저점 gold(R0.77·N58)은 '기준 truth'용 앵커일 뿐 운영값 아님 (큰 범프는 R 높여도 N 충분). → 작은 범프일수록 R 자유도가 없다.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>· 26µm: R=0.37 (N20). R하한 0.2에 여유 있음(0.2면 N37로 더 정밀) → 26µm도 10% 무리없이 달성, 특례 불필요. · 158µm: R=2.2 (N20). R스윕 최저점 gold(26µm R0.2·158µm R0.77)은 기준 truth 앵커일 뿐 운영값 아님.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>■ 설계 원리</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>교호작용→OFAT 불가. [주효과 스윕+의심 교호작용 2×2+같은범프 반복(σ)]. ε=10% 총예산 (2/N)²+(2σ)²≤10² → N_target≈29(26µm은 R하한 탓 N37)·σ≤3.5%. Ground truth 없어 자기참조(gold)+재현성.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>■ 26µm 측정오차 목표: 10%→13%로 완화 (R하한 반영, 잠정)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>R=0.2에서 N=37 → 픽셀화오차 2/N=5.4%가 고정(더 못 내림, R 하한). 총오차=√(5.4²+(2σ)²). 노이즈 2σ~12%(σ~6%, 보통 Frame)면 총 ≈13%. → 26µm은 ε=13%(잠정) 권장, 158µm 등은 10% 유지. 10% 고집 시 σ≤4.2% 강요→Frame·시간 낭비(검사시간 최소화와 충돌). 물리 하한 ~6%(노이즈0)라 5% 이하 불가. 게이지 '허용' 범위 내. 최종값은 Phase2 실측 σ로 √(5.4²+(2σ)²) 확정(노이즈 낮으면 10%로 재조임). 판정 수식도 26µm=±13%, 그 외=±10% 로 반영함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>교호작용(kV×R,W×F,×D)→OFAT 불가. [주효과 스윕+의심 교호작용 2×2+같은범프 반복(σ)]. 픽셀화(R)는 10%(N20)로 통일, 노이즈(σ)는 Frame으로 별도 최소화. Ground truth 없어 자기참조(gold)+재현성.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25"/>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="10">
     <mergeCell ref="A8:H10"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A30:H34"/>
-    <mergeCell ref="A25:H27"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A19:H22"/>
-    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A23:H25"/>
     <mergeCell ref="B6:H6"/>
+    <mergeCell ref="A18:H20"/>
+    <mergeCell ref="A13:H15"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="A13:H16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -647,14 +621,14 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>직경 다이얼(kV)·void 픽셀화(R). gold(최정밀행)=기준 truth 앵커. 26µm gold=R0.2(N37,장비하한) / 158µm gold=R0.77(N58). 고정 F32·W4.</t>
+          <t>직경 다이얼(kV)·void 픽셀화(R). gold(최정밀행)=기준 truth 앵커. N_target=20(ε10% 픽셀화). 고정 F32·W4.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / R≥0.2 · 큰 범프일수록 R↑.</t>
+          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / ε=10%=픽셀화만·N=20통일 / R≥0.2.</t>
         </is>
       </c>
     </row>
@@ -792,7 +766,7 @@
         <v/>
       </c>
       <c r="P6">
-        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=IF(B6="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R6" t="inlineStr">
@@ -843,7 +817,7 @@
         <v/>
       </c>
       <c r="P7">
-        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=IF(B7="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R7" t="inlineStr">
@@ -894,7 +868,7 @@
         <v/>
       </c>
       <c r="P8">
-        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=IF(B8="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R8" t="inlineStr">
@@ -945,7 +919,7 @@
         <v/>
       </c>
       <c r="P9">
-        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=IF(B9="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R9" t="inlineStr">
@@ -996,7 +970,7 @@
         <v/>
       </c>
       <c r="P10">
-        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=IF(B10="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R10" t="inlineStr">
@@ -1047,7 +1021,7 @@
         <v/>
       </c>
       <c r="P11">
-        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=IF(B11="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R11" t="inlineStr">
@@ -1098,12 +1072,12 @@
         <v/>
       </c>
       <c r="P12">
-        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(O12)&lt;=IF(B12="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(O12)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>N≈37 =gold(R하한)</t>
+          <t>N≈37 =gold</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1099,7 @@
         <v>57.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="F13">
         <f>IFERROR(ROUND(C13*0.2828/E13,0),"")</f>
@@ -1149,12 +1123,12 @@
         <v/>
       </c>
       <c r="P13">
-        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(O13)&lt;=IF(B13="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(O13)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>N≈25</t>
+          <t>N≈20 =운영(N20)</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1150,7 @@
         <v>57.5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F14">
         <f>IFERROR(ROUND(C14*0.2828/E14,0),"")</f>
@@ -1200,12 +1174,12 @@
         <v/>
       </c>
       <c r="P14">
-        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(O14)&lt;=IF(B14="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(O14)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>N≈15</t>
+          <t>N≈12</t>
         </is>
       </c>
     </row>
@@ -1251,12 +1225,12 @@
         <v/>
       </c>
       <c r="P15">
-        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(O15)&lt;=IF(B15="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(O15)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>N≈58 =gold(기준앵커)</t>
+          <t>N≈58 =gold</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1252,7 @@
         <v>60.5</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F16">
         <f>IFERROR(ROUND(C16*0.2828/E16,0),"")</f>
@@ -1302,12 +1276,12 @@
         <v/>
       </c>
       <c r="P16">
-        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(O16)&lt;=IF(B16="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(O16)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>N≈30</t>
+          <t>N≈20 =운영(N20)</t>
         </is>
       </c>
     </row>
@@ -1329,7 +1303,7 @@
         <v>60.5</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="F17">
         <f>IFERROR(ROUND(C17*0.2828/E17,0),"")</f>
@@ -1353,12 +1327,12 @@
         <v/>
       </c>
       <c r="P17">
-        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(O17)&lt;=IF(B17="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(O17)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>N≈15</t>
+          <t>N≈13</t>
         </is>
       </c>
     </row>
@@ -1411,14 +1385,14 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>같은 범프 반복→void% σ. 26µm=F스윕(R0.2·W4), 158µm=W스윕(R1.5·F32). kV*.</t>
+          <t>같은 범프 반복→void% σ(노이즈, 10%와 별개). 26µm=F스윕(R0.37·W4), 158µm=W스윕(R2.2·F32). kV*.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / R≥0.2 · 큰 범프일수록 R↑.</t>
+          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / ε=10%=픽셀화만·N=20통일 / R≥0.2.</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1511,7 @@
         <v>57.5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="F6">
         <f>IFERROR(ROUND(C6*0.2828/E6,0),"")</f>
@@ -1561,7 +1535,7 @@
         <v/>
       </c>
       <c r="P6">
-        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=IF(B6="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R6" t="inlineStr">
@@ -1592,7 +1566,7 @@
         <v>57.5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="F7">
         <f>IFERROR(ROUND(C7*0.2828/E7,0),"")</f>
@@ -1616,9 +1590,10 @@
         <v/>
       </c>
       <c r="P7">
-        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=IF(B7="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1638,7 +1613,7 @@
         <v>57.5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="F8">
         <f>IFERROR(ROUND(C8*0.2828/E8,0),"")</f>
@@ -1662,9 +1637,10 @@
         <v/>
       </c>
       <c r="P8">
-        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=IF(B8="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1684,7 +1660,7 @@
         <v>57.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="F9">
         <f>IFERROR(ROUND(C9*0.2828/E9,0),"")</f>
@@ -1708,7 +1684,7 @@
         <v/>
       </c>
       <c r="P9">
-        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=IF(B9="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R9" t="inlineStr">
@@ -1739,7 +1715,7 @@
         <v>57.5</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="F10">
         <f>IFERROR(ROUND(C10*0.2828/E10,0),"")</f>
@@ -1763,9 +1739,10 @@
         <v/>
       </c>
       <c r="P10">
-        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=IF(B10="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1785,7 +1762,7 @@
         <v>57.5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="F11">
         <f>IFERROR(ROUND(C11*0.2828/E11,0),"")</f>
@@ -1809,9 +1786,10 @@
         <v/>
       </c>
       <c r="P11">
-        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=IF(B11="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1831,7 +1809,7 @@
         <v>57.5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="F12">
         <f>IFERROR(ROUND(C12*0.2828/E12,0),"")</f>
@@ -1855,7 +1833,7 @@
         <v/>
       </c>
       <c r="P12">
-        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(O12)&lt;=IF(B12="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(O12)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R12" t="inlineStr">
@@ -1886,7 +1864,7 @@
         <v>57.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="F13">
         <f>IFERROR(ROUND(C13*0.2828/E13,0),"")</f>
@@ -1910,9 +1888,10 @@
         <v/>
       </c>
       <c r="P13">
-        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(O13)&lt;=IF(B13="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(O13)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1932,7 +1911,7 @@
         <v>57.5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="F14">
         <f>IFERROR(ROUND(C14*0.2828/E14,0),"")</f>
@@ -1956,9 +1935,10 @@
         <v/>
       </c>
       <c r="P14">
-        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(O14)&lt;=IF(B14="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(O14)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1978,7 +1958,7 @@
         <v>60.5</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F15">
         <f>IFERROR(ROUND(C15*0.2828/E15,0),"")</f>
@@ -2002,7 +1982,7 @@
         <v/>
       </c>
       <c r="P15">
-        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(O15)&lt;=IF(B15="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(O15)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R15" t="inlineStr">
@@ -2033,7 +2013,7 @@
         <v>60.5</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F16">
         <f>IFERROR(ROUND(C16*0.2828/E16,0),"")</f>
@@ -2057,9 +2037,10 @@
         <v/>
       </c>
       <c r="P16">
-        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(O16)&lt;=IF(B16="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(O16)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2079,7 +2060,7 @@
         <v>60.5</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F17">
         <f>IFERROR(ROUND(C17*0.2828/E17,0),"")</f>
@@ -2103,9 +2084,10 @@
         <v/>
       </c>
       <c r="P17">
-        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(O17)&lt;=IF(B17="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(O17)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2125,7 +2107,7 @@
         <v>60.5</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F18">
         <f>IFERROR(ROUND(C18*0.2828/E18,0),"")</f>
@@ -2149,7 +2131,7 @@
         <v/>
       </c>
       <c r="P18">
-        <f>IF(J18="","",IF(AND(L18="Y",K18&gt;=0.97,K18&lt;=1.03,IFERROR(ABS(O18)&lt;=IF(B18="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J18="","",IF(AND(L18="Y",K18&gt;=0.97,K18&lt;=1.03,IFERROR(ABS(O18)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R18" t="inlineStr">
@@ -2180,7 +2162,7 @@
         <v>60.5</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F19">
         <f>IFERROR(ROUND(C19*0.2828/E19,0),"")</f>
@@ -2204,9 +2186,10 @@
         <v/>
       </c>
       <c r="P19">
-        <f>IF(J19="","",IF(AND(L19="Y",K19&gt;=0.97,K19&lt;=1.03,IFERROR(ABS(O19)&lt;=IF(B19="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J19="","",IF(AND(L19="Y",K19&gt;=0.97,K19&lt;=1.03,IFERROR(ABS(O19)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2226,7 +2209,7 @@
         <v>60.5</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F20">
         <f>IFERROR(ROUND(C20*0.2828/E20,0),"")</f>
@@ -2250,9 +2233,10 @@
         <v/>
       </c>
       <c r="P20">
-        <f>IF(J20="","",IF(AND(L20="Y",K20&gt;=0.97,K20&lt;=1.03,IFERROR(ABS(O20)&lt;=IF(B20="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J20="","",IF(AND(L20="Y",K20&gt;=0.97,K20&lt;=1.03,IFERROR(ABS(O20)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2272,7 +2256,7 @@
         <v>60.5</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F21">
         <f>IFERROR(ROUND(C21*0.2828/E21,0),"")</f>
@@ -2296,7 +2280,7 @@
         <v/>
       </c>
       <c r="P21">
-        <f>IF(J21="","",IF(AND(L21="Y",K21&gt;=0.97,K21&lt;=1.03,IFERROR(ABS(O21)&lt;=IF(B21="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J21="","",IF(AND(L21="Y",K21&gt;=0.97,K21&lt;=1.03,IFERROR(ABS(O21)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R21" t="inlineStr">
@@ -2327,7 +2311,7 @@
         <v>60.5</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F22">
         <f>IFERROR(ROUND(C22*0.2828/E22,0),"")</f>
@@ -2351,9 +2335,10 @@
         <v/>
       </c>
       <c r="P22">
-        <f>IF(J22="","",IF(AND(L22="Y",K22&gt;=0.97,K22&lt;=1.03,IFERROR(ABS(O22)&lt;=IF(B22="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J22="","",IF(AND(L22="Y",K22&gt;=0.97,K22&lt;=1.03,IFERROR(ABS(O22)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2373,7 +2358,7 @@
         <v>60.5</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F23">
         <f>IFERROR(ROUND(C23*0.2828/E23,0),"")</f>
@@ -2397,9 +2382,10 @@
         <v/>
       </c>
       <c r="P23">
-        <f>IF(J23="","",IF(AND(L23="Y",K23&gt;=0.97,K23&lt;=1.03,IFERROR(ABS(O23)&lt;=IF(B23="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J23="","",IF(AND(L23="Y",K23&gt;=0.97,K23&lt;=1.03,IFERROR(ABS(O23)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2419,7 +2405,7 @@
         <v>60.5</v>
       </c>
       <c r="E24" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F24">
         <f>IFERROR(ROUND(C24*0.2828/E24,0),"")</f>
@@ -2443,7 +2429,7 @@
         <v/>
       </c>
       <c r="P24">
-        <f>IF(J24="","",IF(AND(L24="Y",K24&gt;=0.97,K24&lt;=1.03,IFERROR(ABS(O24)&lt;=IF(B24="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J24="","",IF(AND(L24="Y",K24&gt;=0.97,K24&lt;=1.03,IFERROR(ABS(O24)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R24" t="inlineStr">
@@ -2474,7 +2460,7 @@
         <v>60.5</v>
       </c>
       <c r="E25" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F25">
         <f>IFERROR(ROUND(C25*0.2828/E25,0),"")</f>
@@ -2498,9 +2484,10 @@
         <v/>
       </c>
       <c r="P25">
-        <f>IF(J25="","",IF(AND(L25="Y",K25&gt;=0.97,K25&lt;=1.03,IFERROR(ABS(O25)&lt;=IF(B25="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J25="","",IF(AND(L25="Y",K25&gt;=0.97,K25&lt;=1.03,IFERROR(ABS(O25)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2520,7 +2507,7 @@
         <v>60.5</v>
       </c>
       <c r="E26" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F26">
         <f>IFERROR(ROUND(C26*0.2828/E26,0),"")</f>
@@ -2544,9 +2531,10 @@
         <v/>
       </c>
       <c r="P26">
-        <f>IF(J26="","",IF(AND(L26="Y",K26&gt;=0.97,K26&lt;=1.03,IFERROR(ABS(O26)&lt;=IF(B26="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J26="","",IF(AND(L26="Y",K26&gt;=0.97,K26&lt;=1.03,IFERROR(ABS(O26)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R26" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2604,7 +2592,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / R≥0.2 · 큰 범프일수록 R↑.</t>
+          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / ε=10%=픽셀화만·N=20통일 / R≥0.2.</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2735,7 @@
         <v/>
       </c>
       <c r="P6">
-        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=IF(B6="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R6" t="inlineStr">
@@ -2802,9 +2790,10 @@
         <v/>
       </c>
       <c r="P7">
-        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=IF(B7="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2824,7 +2813,7 @@
         <v>55.5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F8">
         <f>IFERROR(ROUND(C8*0.2828/E8,0),"")</f>
@@ -2848,12 +2837,12 @@
         <v/>
       </c>
       <c r="P8">
-        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=IF(B8="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>kV55.5×R0.5(N15)</t>
+          <t>kV55.5×R0.6(N12)</t>
         </is>
       </c>
       <c r="S8">
@@ -2879,7 +2868,7 @@
         <v>55.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F9">
         <f>IFERROR(ROUND(C9*0.2828/E9,0),"")</f>
@@ -2903,9 +2892,10 @@
         <v/>
       </c>
       <c r="P9">
-        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=IF(B9="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2949,7 +2939,7 @@
         <v/>
       </c>
       <c r="P10">
-        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=IF(B10="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R10" t="inlineStr">
@@ -3004,9 +2994,10 @@
         <v/>
       </c>
       <c r="P11">
-        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=IF(B11="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3026,7 +3017,7 @@
         <v>59.5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F12">
         <f>IFERROR(ROUND(C12*0.2828/E12,0),"")</f>
@@ -3050,12 +3041,12 @@
         <v/>
       </c>
       <c r="P12">
-        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(O12)&lt;=IF(B12="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J12="","",IF(AND(L12="Y",K12&gt;=0.97,K12&lt;=1.03,IFERROR(ABS(O12)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>kV59.5×R0.5(N15)</t>
+          <t>kV59.5×R0.6(N12)</t>
         </is>
       </c>
       <c r="S12">
@@ -3081,7 +3072,7 @@
         <v>59.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F13">
         <f>IFERROR(ROUND(C13*0.2828/E13,0),"")</f>
@@ -3105,9 +3096,10 @@
         <v/>
       </c>
       <c r="P13">
-        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(O13)&lt;=IF(B13="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J13="","",IF(AND(L13="Y",K13&gt;=0.97,K13&lt;=1.03,IFERROR(ABS(O13)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3127,7 +3119,7 @@
         <v>60.5</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F14">
         <f>IFERROR(ROUND(C14*0.2828/E14,0),"")</f>
@@ -3151,7 +3143,7 @@
         <v/>
       </c>
       <c r="P14">
-        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(O14)&lt;=IF(B14="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J14="","",IF(AND(L14="Y",K14&gt;=0.97,K14&lt;=1.03,IFERROR(ABS(O14)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R14" t="inlineStr">
@@ -3182,7 +3174,7 @@
         <v>60.5</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F15">
         <f>IFERROR(ROUND(C15*0.2828/E15,0),"")</f>
@@ -3206,9 +3198,10 @@
         <v/>
       </c>
       <c r="P15">
-        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(O15)&lt;=IF(B15="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J15="","",IF(AND(L15="Y",K15&gt;=0.97,K15&lt;=1.03,IFERROR(ABS(O15)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3228,7 +3221,7 @@
         <v>60.5</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F16">
         <f>IFERROR(ROUND(C16*0.2828/E16,0),"")</f>
@@ -3252,7 +3245,7 @@
         <v/>
       </c>
       <c r="P16">
-        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(O16)&lt;=IF(B16="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J16="","",IF(AND(L16="Y",K16&gt;=0.97,K16&lt;=1.03,IFERROR(ABS(O16)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R16" t="inlineStr">
@@ -3283,7 +3276,7 @@
         <v>60.5</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F17">
         <f>IFERROR(ROUND(C17*0.2828/E17,0),"")</f>
@@ -3307,9 +3300,10 @@
         <v/>
       </c>
       <c r="P17">
-        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(O17)&lt;=IF(B17="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J17="","",IF(AND(L17="Y",K17&gt;=0.97,K17&lt;=1.03,IFERROR(ABS(O17)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3329,7 +3323,7 @@
         <v>60.5</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F18">
         <f>IFERROR(ROUND(C18*0.2828/E18,0),"")</f>
@@ -3353,7 +3347,7 @@
         <v/>
       </c>
       <c r="P18">
-        <f>IF(J18="","",IF(AND(L18="Y",K18&gt;=0.97,K18&lt;=1.03,IFERROR(ABS(O18)&lt;=IF(B18="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J18="","",IF(AND(L18="Y",K18&gt;=0.97,K18&lt;=1.03,IFERROR(ABS(O18)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R18" t="inlineStr">
@@ -3384,7 +3378,7 @@
         <v>60.5</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F19">
         <f>IFERROR(ROUND(C19*0.2828/E19,0),"")</f>
@@ -3408,9 +3402,10 @@
         <v/>
       </c>
       <c r="P19">
-        <f>IF(J19="","",IF(AND(L19="Y",K19&gt;=0.97,K19&lt;=1.03,IFERROR(ABS(O19)&lt;=IF(B19="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J19="","",IF(AND(L19="Y",K19&gt;=0.97,K19&lt;=1.03,IFERROR(ABS(O19)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3430,7 +3425,7 @@
         <v>60.5</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F20">
         <f>IFERROR(ROUND(C20*0.2828/E20,0),"")</f>
@@ -3454,7 +3449,7 @@
         <v/>
       </c>
       <c r="P20">
-        <f>IF(J20="","",IF(AND(L20="Y",K20&gt;=0.97,K20&lt;=1.03,IFERROR(ABS(O20)&lt;=IF(B20="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J20="","",IF(AND(L20="Y",K20&gt;=0.97,K20&lt;=1.03,IFERROR(ABS(O20)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R20" t="inlineStr">
@@ -3485,7 +3480,7 @@
         <v>60.5</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F21">
         <f>IFERROR(ROUND(C21*0.2828/E21,0),"")</f>
@@ -3509,9 +3504,10 @@
         <v/>
       </c>
       <c r="P21">
-        <f>IF(J21="","",IF(AND(L21="Y",K21&gt;=0.97,K21&lt;=1.03,IFERROR(ABS(O21)&lt;=IF(B21="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J21="","",IF(AND(L21="Y",K21&gt;=0.97,K21&lt;=1.03,IFERROR(ABS(O21)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R21" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3562,14 +3558,14 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>모델 산출 (kV,R,F,W)로 자재별 ×3반복. 합격: 매칭Y &amp; Q_dia97~103% &amp; |void편차|≤10% &amp; σ≤3.5% &amp; tact 최소.</t>
+          <t>모델 산출 (kV,R,F,W)로 자재별 ×3반복. 합격: 매칭Y &amp; Q_dia97~103% &amp; |void편차|≤10% &amp; σ(별도) 최소 &amp; tact 최소.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / R≥0.2 · 큰 범프일수록 R↑.</t>
+          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / ε=10%=픽셀화만·N=20통일 / R≥0.2.</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3687,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(모델R≥0.2)</t>
+          <t>(모델R≈0.37)</t>
         </is>
       </c>
       <c r="F6">
@@ -3718,7 +3714,7 @@
         <v/>
       </c>
       <c r="P6">
-        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=IF(B6="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J6="","",IF(AND(L6="Y",K6&gt;=0.97,K6&lt;=1.03,IFERROR(ABS(O6)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R6" t="inlineStr">
@@ -3752,7 +3748,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(모델R≥0.2)</t>
+          <t>(모델R≈0.37)</t>
         </is>
       </c>
       <c r="F7">
@@ -3779,9 +3775,10 @@
         <v/>
       </c>
       <c r="P7">
-        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=IF(B7="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J7="","",IF(AND(L7="Y",K7&gt;=0.97,K7&lt;=1.03,IFERROR(ABS(O7)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3804,7 +3801,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(모델R≥0.2)</t>
+          <t>(모델R≈0.37)</t>
         </is>
       </c>
       <c r="F8">
@@ -3831,9 +3828,10 @@
         <v/>
       </c>
       <c r="P8">
-        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=IF(B8="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J8="","",IF(AND(L8="Y",K8&gt;=0.97,K8&lt;=1.03,IFERROR(ABS(O8)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3856,7 +3854,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(모델R,높음)</t>
+          <t>(모델R≈2.2)</t>
         </is>
       </c>
       <c r="F9">
@@ -3883,7 +3881,7 @@
         <v/>
       </c>
       <c r="P9">
-        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=IF(B9="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
+        <f>IF(J9="","",IF(AND(L9="Y",K9&gt;=0.97,K9&lt;=1.03,IFERROR(ABS(O9)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
         <v/>
       </c>
       <c r="R9" t="inlineStr">
@@ -3917,7 +3915,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(모델R,높음)</t>
+          <t>(모델R≈2.2)</t>
         </is>
       </c>
       <c r="F10">
@@ -3944,9 +3942,10 @@
         <v/>
       </c>
       <c r="P10">
-        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=IF(B10="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J10="","",IF(AND(L10="Y",K10&gt;=0.97,K10&lt;=1.03,IFERROR(ABS(O10)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3969,7 +3968,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(모델R,높음)</t>
+          <t>(모델R≈2.2)</t>
         </is>
       </c>
       <c r="F11">
@@ -3996,9 +3995,10 @@
         <v/>
       </c>
       <c r="P11">
-        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=IF(B11="26µm",0.13,0.1),FALSE)),"PASS","FAIL"))</f>
-        <v/>
-      </c>
+        <f>IF(J11="","",IF(AND(L11="Y",K11&gt;=0.97,K11&lt;=1.03,IFERROR(ABS(O11)&lt;=0.1,FALSE)),"PASS","FAIL"))</f>
+        <v/>
+      </c>
+      <c r="R11" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4057,12 +4057,12 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>N_target(R)</t>
+          <t>N_target</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Phase1 R스윕: gold 대비 |void편차| 7% 넘는 N(≈29). 26µm은 R하한→N37 고정(R0.2)</t>
+          <t>ε=10% 픽셀화 → N=2/ε=20 (전 자재 통일). Phase1 R스윕으로 검증</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Phase2 F스윕: void% σ_rel≤3.5% 최소 F</t>
+          <t>Phase2 F스윕: 노이즈 재현성 σ 최소화(10%와 별개 축). 최소 Frame 확정</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>tact=a·(shot수·F)+b. 26µm은 R고정→shot수·F로만 단축</t>
+          <t>tact=a·(shot수·F)+b. shot수=ROUNDUP(목표범프/(R²비례))</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>R = max(0.2, D·√p/N_target). 큰 범프일수록 R↑ / 작은 범프는 0.2에 걸림</t>
+          <t>R = max(0.2, D·√p/20). 큰 범프일수록 R↑ / 26µm는 0.37</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>σ(F)에서 σ_rel≤3.5% 최소 F</t>
+          <t>σ(F)에서 목표 σ 되는 최소 F (노이즈 축, 10%와 별개)</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>※ 확정 계수는 레시피모델.xlsx·파라미터_계산기.xlsx 보정계수·N_target에 옮겨 완성.</t>
+          <t>※ 확정 계수는 레시피모델.xlsx·파라미터_계산기.xlsx 보정계수·N_target(=20)에 옮겨 완성.</t>
         </is>
       </c>
     </row>

--- a/계산모델_엑셀/공정모델링_실험런시트_55런.xlsx
+++ b/계산모델_엑셀/공정모델링_실험런시트_55런.xlsx
@@ -511,7 +511,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>XRA_VOID.csv: 범프 Area = π/4·(측정직경)² 정확 일치 → void% = void면적÷측정면적, 8% 판정도 여기 적용. 런시트는 장비 출력 void%(M열) 그대로 입력. 이 관계는 측정직경=PD(Q_dia=100%)일 때만 성립 → 그래서 kV를 먼저 맞춤.</t>
+          <t>XRA_VOID.csv: 범프 Area = π/4·(측정직경)² 정확 일치 → void% = void면적÷측정면적, 8% 판정도 여기 적용. 이 관계는 측정직경=PD(Q_dia=100%)일 때만 성립 → 그래서 kV를 먼저 맞춤.</t>
         </is>
       </c>
     </row>
@@ -527,23 +527,23 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>void 면적 픽셀화오차 ≈ 2/N. ε=10%로 두면 N=20. 노이즈는 이 10%에 미포함 — Frame으로 σ 별도 관리(정밀도 축 분리). 파라미터_계산기·레시피모델(N_target=20)과 동일 기준. R = √p·D/20 = 0.0141·D → 큰 범프일수록 R↑.</t>
+          <t>void 면적 픽셀화오차 ≈ 2/N. ε=10%→N=20. 노이즈는 이 10%에 미포함 — Frame으로 σ 별도 관리. 파라미터_계산기·레시피모델(N=20)과 동일. R = √p·D/20 = 0.0141·D → 큰 범프일수록 R↑.</t>
         </is>
       </c>
     </row>
     <row r="14"/>
     <row r="15"/>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>■ 자재별 R (운영값, N=20)</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ 장비 제약: R≥0.2 µm/px, Frame≥32 (그 이하 불가) ★</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>· 26µm: R=0.37 (N20). R하한 0.2에 여유 있음(0.2면 N37로 더 정밀) → 26µm도 10% 무리없이 달성, 특례 불필요. · 158µm: R=2.2 (N20). R스윕 최저점 gold(26µm R0.2·158µm R0.77)은 기준 truth 앵커일 뿐 운영값 아님.</t>
+          <t>· R: 26µm 운영 R=0.37(N20, 하한 0.2에 여유), 158µm R=2.2(N20). gold(26µm R0.2·158µm R0.77)은 기준 앵커. · Frame: 최소 32. F 스윕은 32→64→128(상향)으로 '32로 충분한가'를 확인(더 낮출 수 없음).</t>
         </is>
       </c>
     </row>
@@ -559,14 +559,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>교호작용(kV×R,W×F,×D)→OFAT 불가. [주효과 스윕+의심 교호작용 2×2+같은범프 반복(σ)]. 픽셀화(R)는 10%(N20)로 통일, 노이즈(σ)는 Frame으로 별도 최소화. Ground truth 없어 자기참조(gold)+재현성.</t>
+          <t>교호작용→OFAT 불가. [주효과 스윕+의심 교호작용 2×2+같은범프 반복(σ)]. 픽셀화(R)는 N20 통일, 노이즈(σ)는 Frame으로 별도. Ground truth 없어 자기참조(gold)+재현성.</t>
         </is>
       </c>
     </row>
     <row r="24"/>
     <row r="25"/>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A8:H10"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A12:H12"/>
@@ -577,6 +577,7 @@
     <mergeCell ref="A18:H20"/>
     <mergeCell ref="A13:H15"/>
     <mergeCell ref="B5:H5"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -621,14 +622,14 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>직경 다이얼(kV)·void 픽셀화(R). gold(최정밀행)=기준 truth 앵커. N_target=20(ε10% 픽셀화). 고정 F32·W4.</t>
+          <t>직경 다이얼(kV)·void 픽셀화(R). gold=기준 앵커. N_target=20. 고정 F32·W4.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / ε=10%=픽셀화만·N=20통일 / R≥0.2.</t>
+          <t>D(C열)=PD직경(독립) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / N=20통일 / R≥0.2 · F≥32.</t>
         </is>
       </c>
     </row>
@@ -1385,14 +1386,14 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>같은 범프 반복→void% σ(노이즈, 10%와 별개). 26µm=F스윕(R0.37·W4), 158µm=W스윕(R2.2·F32). kV*.</t>
+          <t>같은 범프 반복→void% σ(노이즈, 10%와 별개). F는 32부터(장비 최소). 26µm=F스윕(R0.37·W4), 158µm=W스윕(R2.2·F32). kV*.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / ε=10%=픽셀화만·N=20통일 / R≥0.2.</t>
+          <t>D(C열)=PD직경(독립) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / N=20통일 / R≥0.2 · F≥32.</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1497,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F16</t>
+          <t>F32</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1518,7 +1519,7 @@
         <v/>
       </c>
       <c r="G6" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
@@ -1540,7 +1541,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>F=16 재현성</t>
+          <t>F=32 재현성</t>
         </is>
       </c>
       <c r="S6">
@@ -1551,7 +1552,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F16</t>
+          <t>F32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1573,7 +1574,7 @@
         <v/>
       </c>
       <c r="G7" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H7" t="n">
         <v>4</v>
@@ -1598,7 +1599,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F16</t>
+          <t>F32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1620,7 +1621,7 @@
         <v/>
       </c>
       <c r="G8" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H8" t="n">
         <v>4</v>
@@ -1645,7 +1646,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F32</t>
+          <t>F64</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1667,7 +1668,7 @@
         <v/>
       </c>
       <c r="G9" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
@@ -1689,7 +1690,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>F=32 재현성</t>
+          <t>F=64 재현성</t>
         </is>
       </c>
       <c r="S9">
@@ -1700,7 +1701,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F32</t>
+          <t>F64</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1722,7 +1723,7 @@
         <v/>
       </c>
       <c r="G10" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H10" t="n">
         <v>4</v>
@@ -1747,7 +1748,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F32</t>
+          <t>F64</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1769,7 +1770,7 @@
         <v/>
       </c>
       <c r="G11" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H11" t="n">
         <v>4</v>
@@ -1794,7 +1795,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F64</t>
+          <t>F128</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1816,7 +1817,7 @@
         <v/>
       </c>
       <c r="G12" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="H12" t="n">
         <v>4</v>
@@ -1838,7 +1839,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>F=64 재현성</t>
+          <t>F=128 재현성</t>
         </is>
       </c>
       <c r="S12">
@@ -1849,7 +1850,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F64</t>
+          <t>F128</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1871,7 +1872,7 @@
         <v/>
       </c>
       <c r="G13" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="H13" t="n">
         <v>4</v>
@@ -1896,7 +1897,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F64</t>
+          <t>F128</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1918,7 +1919,7 @@
         <v/>
       </c>
       <c r="G14" t="n">
-        <v>64</v>
+        <v>128</v>
       </c>
       <c r="H14" t="n">
         <v>4</v>
@@ -2585,14 +2586,14 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>kV×R(26µm): 대비bias×픽셀화 / W×F(158µm): SNR∝√(W·F) 교환. ×D는 두 자재.</t>
+          <t>kV×R(26µm): 대비bias×픽셀화 / W×F(158µm): SNR∝√(W·F) 교환(F≥32). ×D는 두 자재.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / ε=10%=픽셀화만·N=20통일 / R≥0.2.</t>
+          <t>D(C열)=PD직경(독립) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / N=20통일 / R≥0.2 · F≥32.</t>
         </is>
       </c>
     </row>
@@ -3126,7 +3127,7 @@
         <v/>
       </c>
       <c r="G14" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H14" t="n">
         <v>4</v>
@@ -3148,7 +3149,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>W4×F16</t>
+          <t>W4×F32</t>
         </is>
       </c>
       <c r="S14">
@@ -3181,7 +3182,7 @@
         <v/>
       </c>
       <c r="G15" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H15" t="n">
         <v>4</v>
@@ -3228,7 +3229,7 @@
         <v/>
       </c>
       <c r="G16" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H16" t="n">
         <v>4</v>
@@ -3250,7 +3251,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>W4×F32</t>
+          <t>W4×F64</t>
         </is>
       </c>
       <c r="S16">
@@ -3283,7 +3284,7 @@
         <v/>
       </c>
       <c r="G17" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H17" t="n">
         <v>4</v>
@@ -3330,7 +3331,7 @@
         <v/>
       </c>
       <c r="G18" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H18" t="n">
         <v>6</v>
@@ -3352,7 +3353,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>W6×F16</t>
+          <t>W6×F32</t>
         </is>
       </c>
       <c r="S18">
@@ -3385,7 +3386,7 @@
         <v/>
       </c>
       <c r="G19" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H19" t="n">
         <v>6</v>
@@ -3432,7 +3433,7 @@
         <v/>
       </c>
       <c r="G20" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H20" t="n">
         <v>6</v>
@@ -3454,7 +3455,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>W6×F32</t>
+          <t>W6×F64</t>
         </is>
       </c>
       <c r="S20">
@@ -3487,7 +3488,7 @@
         <v/>
       </c>
       <c r="G21" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="H21" t="n">
         <v>6</v>
@@ -3565,7 +3566,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>D(C열)=PD직경(독립·참값) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / ε=10%=픽셀화만·N=20통일 / R≥0.2.</t>
+          <t>D(C열)=PD직경(독립) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / N=20통일 / R≥0.2 · F≥32.</t>
         </is>
       </c>
     </row>
@@ -3694,8 +3695,10 @@
         <f>IFERROR(ROUND(C6*0.2828/E6,0),"")</f>
         <v/>
       </c>
-      <c r="G6" t="n">
-        <v>32</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>(모델F≥32)</t>
+        </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -3755,8 +3758,10 @@
         <f>IFERROR(ROUND(C7*0.2828/E7,0),"")</f>
         <v/>
       </c>
-      <c r="G7" t="n">
-        <v>32</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>(모델F≥32)</t>
+        </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -3808,8 +3813,10 @@
         <f>IFERROR(ROUND(C8*0.2828/E8,0),"")</f>
         <v/>
       </c>
-      <c r="G8" t="n">
-        <v>32</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>(모델F≥32)</t>
+        </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -3861,8 +3868,10 @@
         <f>IFERROR(ROUND(C9*0.2828/E9,0),"")</f>
         <v/>
       </c>
-      <c r="G9" t="n">
-        <v>32</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>(모델F≥32)</t>
+        </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -3922,8 +3931,10 @@
         <f>IFERROR(ROUND(C10*0.2828/E10,0),"")</f>
         <v/>
       </c>
-      <c r="G10" t="n">
-        <v>32</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>(모델F≥32)</t>
+        </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -3975,8 +3986,10 @@
         <f>IFERROR(ROUND(C11*0.2828/E11,0),"")</f>
         <v/>
       </c>
-      <c r="G11" t="n">
-        <v>32</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>(모델F≥32)</t>
+        </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -4062,19 +4075,19 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>ε=10% 픽셀화 → N=2/ε=20 (전 자재 통일). Phase1 R스윕으로 검증</t>
+          <t>ε=10% 픽셀화 → N=20 통일. Phase1 R스윕 검증</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>σ(F)</t>
+          <t>F_min</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Phase2 F스윕: 노이즈 재현성 σ 최소화(10%와 별개 축). 최소 Frame 확정</t>
+          <t>Phase2 F스윕(32·64·128): 목표 σ 되는 최소 Frame. 장비 하한 32</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4123,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>tact=a·(shot수·F)+b. shot수=ROUNDUP(목표범프/(R²비례))</t>
+          <t>tact=a·(shot수·F)+b</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4166,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>R = max(0.2, D·√p/20). 큰 범프일수록 R↑ / 26µm는 0.37</t>
+          <t>R = max(0.2, D·√p/20). 26µm는 0.37</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4178,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>σ(F)에서 목표 σ 되는 최소 F (노이즈 축, 10%와 별개)</t>
+          <t>max(32, σ목표 되는 최소 Frame). 장비 하한 32</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4190,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>얇으면 4W, 두꺼우면 W*(D). W↑로 F↓ 교환</t>
+          <t>얇으면 4W, 두꺼우면 W*(D). W↑로 F↓ 교환(단 32까지)</t>
         </is>
       </c>
     </row>

--- a/계산모델_엑셀/공정모델링_실험런시트_55런.xlsx
+++ b/계산모델_엑셀/공정모델링_실험런시트_55런.xlsx
@@ -64,13 +64,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -443,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -466,7 +469,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>목표: 모델 구축 시 [PD직경 D 입력] → [최적 kV·R·F·W 자동 결정] 으로 측정직경=100%·void 면적오차≤ε·검사시간 최소.</t>
+          <t>대원칙: 정확한 검사결과가 최우선 제약. 시간단축은 '정확도를 지키는 범위 안에서만' 한다(정확도를 시간과 바꾸지 않음).</t>
         </is>
       </c>
     </row>
@@ -483,7 +486,7 @@
           <t>① PD직경 D (독립변수)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>PD로 확인한 실제 범프 직경. 자재 고유·고정(26·158µm). N 설계·자재 구분 기준.</t>
         </is>
@@ -495,7 +498,7 @@
           <t>② 측정직경 (종속변수)</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>X-ray 검사 결과 직경. kV 등에 따라 변함. 목표는 PD직경의 100%(Q_dia).</t>
         </is>
@@ -509,75 +512,123 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>XRA_VOID.csv: 범프 Area = π/4·(측정직경)² 정확 일치 → void% = void면적÷측정면적, 8% 판정도 여기 적용. 이 관계는 측정직경=PD(Q_dia=100%)일 때만 성립 → 그래서 kV를 먼저 맞춤.</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>XRA_VOID.csv: 범프 Area=π/4·(측정직경)² → void%=void면적÷측정면적. 측정직경=PD(Q_dia=100%)일 때만 성립 → kV 먼저 맞춤.</t>
         </is>
       </c>
     </row>
     <row r="9"/>
-    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 정확도 정의 = void 총오차 ≤ 10% (픽셀화 ⊕ 노이즈, 제곱합) ★</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>■ 측정오차 ε=10% = '픽셀화(해상도)만' → N=2/ε=20 (전 자재 통일) ★</t>
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>총오차 = √( 평균편차² + (2σ)² ) ≤ 10%. 두 성분을 함께 만족해야 '정확'.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>void 면적 픽셀화오차 ≈ 2/N. ε=10%→N=20. 노이즈는 이 10%에 미포함 — Frame으로 σ 별도 관리. 파라미터_계산기·레시피모델(N=20)과 동일. R = √p·D/20 = 0.0141·D → 큰 범프일수록 R↑.</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>· 픽셀화(R): 2/N ≤ ~7% → N_target≈29 (여유 확보). ※ N=20은 픽셀화만으로 10%를 다 써 노이즈 더하면 초과=부정확 → 폐기. · 노이즈(F,W): 2σ ≤ ~7% → σ≤3.5%, Frame으로 확보(F≥32).</t>
         </is>
       </c>
     </row>
     <row r="14"/>
     <row r="15"/>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>■ 장비 제약: R≥0.2 µm/px, Frame≥32 (그 이하 불가) ★</t>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>■ 시간단축 지렛대와 '정확도 한계'</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>· R: 26µm 운영 R=0.37(N20, 하한 0.2에 여유), 158µm R=2.2(N20). gold(26µm R0.2·158µm R0.77)은 기준 앵커. · Frame: 최소 32. F 스윕은 32→64→128(상향)으로 '32로 충분한가'를 확인(더 낮출 수 없음).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>■ 설계 원리</t>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>R 크게=빠름</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>N29 주는 R까지만 (26µm 0.25·158µm 1.5). 더 키우면 픽셀화 초과=부정확</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>F 작게=빠름</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>σ 지키는 F까지만 (장비 하한 32). 더 낮추면 노이즈 초과=부정확</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>shot 적게=빠름</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>per-bump 측정과 무관 → 정확도 안전한 지렛대. 단 표본수·타일 일관성 유지</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>W (두꺼운)</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>블러(경계폭)·Q_dia 가드 지키는 선에서만</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>교호작용→OFAT 불가. [주효과 스윕+의심 교호작용 2×2+같은범프 반복(σ)]. 픽셀화(R)는 N20 통일, 노이즈(σ)는 Frame으로 별도. Ground truth 없어 자기참조(gold)+재현성.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>■ 자재별 결론</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>· 26µm: 정확도가 R(0.2~0.25)·F(≥32)를 거의 고정 → 시간여유 적음. 그래도 정확도 우선이라 그대로 감. 남은 안전한 시간지렛대는 shot(검사범프)수. · 158µm: R(1.5)·F에 여유 있어 시간최적 폭 큼.</t>
+        </is>
+      </c>
+    </row>
     <row r="25"/>
+    <row r="26"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A8:H10"/>
+  <mergeCells count="14">
+    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="B18:H18"/>
     <mergeCell ref="A7:H7"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="B21:H21"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A23:H25"/>
+    <mergeCell ref="A24:H26"/>
     <mergeCell ref="B6:H6"/>
-    <mergeCell ref="A18:H20"/>
+    <mergeCell ref="A11:H11"/>
     <mergeCell ref="A13:H15"/>
     <mergeCell ref="B5:H5"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="A8:H9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -609,7 +660,7 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -620,106 +671,106 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>직경 다이얼(kV)·void 픽셀화(R). gold=기준 앵커. N_target=20. 고정 F32·W4.</t>
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>직경 다이얼(kV)·void 픽셀화(R). gold=기준 앵커. N_target≈29(총오차 예산). 고정 F32·W4.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>D(C열)=PD직경(독립) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / N=20통일 / R≥0.2 · F≥32.</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>정확도=총오차≤10%(픽셀화⊕노이즈). N_target≈29 · R≥0.2 · F≥32. D=PD직경(독립)/측정직경=종속/void%=장비출력(측정면적).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>자재</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>PD직경 D(µm)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>R(µm/px)</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>N(자동)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>반복#</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>측정직경(µm)</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>Q_dia(자동)=측정÷PD</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>매칭(Y/N)</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>void%(측정,장비값)</t>
         </is>
       </c>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>기준gold void%</t>
         </is>
       </c>
-      <c r="O5" s="6" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>void편차%(자동)</t>
         </is>
       </c>
-      <c r="P5" s="6" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>판정(자동)</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="7" t="inlineStr">
         <is>
           <t>tact(초)</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
@@ -1100,7 +1151,7 @@
         <v>57.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="F13">
         <f>IFERROR(ROUND(C13*0.2828/E13,0),"")</f>
@@ -1129,7 +1180,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>N≈20 =운영(N20)</t>
+          <t>N≈29 =운영(N29)</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1202,7 @@
         <v>57.5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F14">
         <f>IFERROR(ROUND(C14*0.2828/E14,0),"")</f>
@@ -1180,7 +1231,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>N≈12</t>
+          <t>N≈15</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1304,7 @@
         <v>60.5</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F16">
         <f>IFERROR(ROUND(C16*0.2828/E16,0),"")</f>
@@ -1282,7 +1333,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>N≈20 =운영(N20)</t>
+          <t>N≈30 =운영(N29)</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1355,7 @@
         <v>60.5</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="F17">
         <f>IFERROR(ROUND(C17*0.2828/E17,0),"")</f>
@@ -1333,7 +1384,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>N≈13</t>
+          <t>N≈15</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1372,8 +1423,9 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1384,113 +1436,118 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>같은 범프 반복→void% σ(노이즈, 10%와 별개). F는 32부터(장비 최소). 26µm=F스윕(R0.37·W4), 158µm=W스윕(R2.2·F32). kV*.</t>
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>같은 범프 반복→void% σ(노이즈). 총오차=√(편차²+(2σ)²)≤10% 확인. 26µm=F스윕(R0.25·W4), 158µm=W스윕(R1.5·F32). F≥32.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>D(C열)=PD직경(독립) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / N=20통일 / R≥0.2 · F≥32.</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>정확도=총오차≤10%(픽셀화⊕노이즈). N_target≈29 · R≥0.2 · F≥32. D=PD직경(독립)/측정직경=종속/void%=장비출력(측정면적).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>자재</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>PD직경 D(µm)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>R(µm/px)</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>N(자동)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>반복#</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>측정직경(µm)</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>Q_dia(자동)=측정÷PD</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>매칭(Y/N)</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>void%(측정,장비값)</t>
         </is>
       </c>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>기준gold void%</t>
         </is>
       </c>
-      <c r="O5" s="6" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>void편차%(자동)</t>
         </is>
       </c>
-      <c r="P5" s="6" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>판정(자동)</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="7" t="inlineStr">
         <is>
           <t>tact(초)</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
-      <c r="S5" s="6" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>void%σ_rel(자동)</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>총오차_rel(자동)≤0.10</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1569,7 @@
         <v>57.5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="F6">
         <f>IFERROR(ROUND(C6*0.2828/E6,0),"")</f>
@@ -1541,13 +1598,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>F=32 재현성</t>
+          <t>F=32 재현성·총오차</t>
         </is>
       </c>
       <c r="S6">
         <f>IFERROR(STDEV(M6:M8)/AVERAGE(M6:M8),"")</f>
         <v/>
       </c>
+      <c r="T6">
+        <f>IFERROR(SQRT(((AVERAGE(M6:M8)-N6)/N6)^2+(2*STDEV(M6:M8)/AVERAGE(M6:M8))^2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1567,7 +1628,7 @@
         <v>57.5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="F7">
         <f>IFERROR(ROUND(C7*0.2828/E7,0),"")</f>
@@ -1614,7 +1675,7 @@
         <v>57.5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="F8">
         <f>IFERROR(ROUND(C8*0.2828/E8,0),"")</f>
@@ -1661,7 +1722,7 @@
         <v>57.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="F9">
         <f>IFERROR(ROUND(C9*0.2828/E9,0),"")</f>
@@ -1690,13 +1751,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>F=64 재현성</t>
+          <t>F=64 재현성·총오차</t>
         </is>
       </c>
       <c r="S9">
         <f>IFERROR(STDEV(M9:M11)/AVERAGE(M9:M11),"")</f>
         <v/>
       </c>
+      <c r="T9">
+        <f>IFERROR(SQRT(((AVERAGE(M9:M11)-N9)/N9)^2+(2*STDEV(M9:M11)/AVERAGE(M9:M11))^2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1716,7 +1781,7 @@
         <v>57.5</v>
       </c>
       <c r="E10" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="F10">
         <f>IFERROR(ROUND(C10*0.2828/E10,0),"")</f>
@@ -1763,7 +1828,7 @@
         <v>57.5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="F11">
         <f>IFERROR(ROUND(C11*0.2828/E11,0),"")</f>
@@ -1810,7 +1875,7 @@
         <v>57.5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="F12">
         <f>IFERROR(ROUND(C12*0.2828/E12,0),"")</f>
@@ -1839,13 +1904,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>F=128 재현성</t>
+          <t>F=128 재현성·총오차</t>
         </is>
       </c>
       <c r="S12">
         <f>IFERROR(STDEV(M12:M14)/AVERAGE(M12:M14),"")</f>
         <v/>
       </c>
+      <c r="T12">
+        <f>IFERROR(SQRT(((AVERAGE(M12:M14)-N12)/N12)^2+(2*STDEV(M12:M14)/AVERAGE(M12:M14))^2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1865,7 +1934,7 @@
         <v>57.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="F13">
         <f>IFERROR(ROUND(C13*0.2828/E13,0),"")</f>
@@ -1912,7 +1981,7 @@
         <v>57.5</v>
       </c>
       <c r="E14" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="F14">
         <f>IFERROR(ROUND(C14*0.2828/E14,0),"")</f>
@@ -1959,7 +2028,7 @@
         <v>60.5</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F15">
         <f>IFERROR(ROUND(C15*0.2828/E15,0),"")</f>
@@ -1995,6 +2064,10 @@
         <f>IFERROR(STDEV(M15:M17)/AVERAGE(M15:M17),"")</f>
         <v/>
       </c>
+      <c r="T15">
+        <f>IFERROR(SQRT(((AVERAGE(M15:M17)-N15)/N15)^2+(2*STDEV(M15:M17)/AVERAGE(M15:M17))^2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2014,7 +2087,7 @@
         <v>60.5</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F16">
         <f>IFERROR(ROUND(C16*0.2828/E16,0),"")</f>
@@ -2061,7 +2134,7 @@
         <v>60.5</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F17">
         <f>IFERROR(ROUND(C17*0.2828/E17,0),"")</f>
@@ -2108,7 +2181,7 @@
         <v>60.5</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F18">
         <f>IFERROR(ROUND(C18*0.2828/E18,0),"")</f>
@@ -2144,6 +2217,10 @@
         <f>IFERROR(STDEV(M18:M20)/AVERAGE(M18:M20),"")</f>
         <v/>
       </c>
+      <c r="T18">
+        <f>IFERROR(SQRT(((AVERAGE(M18:M20)-N18)/N18)^2+(2*STDEV(M18:M20)/AVERAGE(M18:M20))^2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2163,7 +2240,7 @@
         <v>60.5</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F19">
         <f>IFERROR(ROUND(C19*0.2828/E19,0),"")</f>
@@ -2210,7 +2287,7 @@
         <v>60.5</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F20">
         <f>IFERROR(ROUND(C20*0.2828/E20,0),"")</f>
@@ -2257,7 +2334,7 @@
         <v>60.5</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F21">
         <f>IFERROR(ROUND(C21*0.2828/E21,0),"")</f>
@@ -2293,6 +2370,10 @@
         <f>IFERROR(STDEV(M21:M23)/AVERAGE(M21:M23),"")</f>
         <v/>
       </c>
+      <c r="T21">
+        <f>IFERROR(SQRT(((AVERAGE(M21:M23)-N21)/N21)^2+(2*STDEV(M21:M23)/AVERAGE(M21:M23))^2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2312,7 +2393,7 @@
         <v>60.5</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F22">
         <f>IFERROR(ROUND(C22*0.2828/E22,0),"")</f>
@@ -2359,7 +2440,7 @@
         <v>60.5</v>
       </c>
       <c r="E23" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F23">
         <f>IFERROR(ROUND(C23*0.2828/E23,0),"")</f>
@@ -2406,7 +2487,7 @@
         <v>60.5</v>
       </c>
       <c r="E24" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F24">
         <f>IFERROR(ROUND(C24*0.2828/E24,0),"")</f>
@@ -2442,6 +2523,10 @@
         <f>IFERROR(STDEV(M24:M26)/AVERAGE(M24:M26),"")</f>
         <v/>
       </c>
+      <c r="T24">
+        <f>IFERROR(SQRT(((AVERAGE(M24:M26)-N24)/N24)^2+(2*STDEV(M24:M26)/AVERAGE(M24:M26))^2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2461,7 +2546,7 @@
         <v>60.5</v>
       </c>
       <c r="E25" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F25">
         <f>IFERROR(ROUND(C25*0.2828/E25,0),"")</f>
@@ -2508,7 +2593,7 @@
         <v>60.5</v>
       </c>
       <c r="E26" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F26">
         <f>IFERROR(ROUND(C26*0.2828/E26,0),"")</f>
@@ -2552,7 +2637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S21"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2572,8 +2657,9 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2584,113 +2670,118 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>kV×R(26µm): 대비bias×픽셀화 / W×F(158µm): SNR∝√(W·F) 교환(F≥32). ×D는 두 자재.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>D(C열)=PD직경(독립) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / N=20통일 / R≥0.2 · F≥32.</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>정확도=총오차≤10%(픽셀화⊕노이즈). N_target≈29 · R≥0.2 · F≥32. D=PD직경(독립)/측정직경=종속/void%=장비출력(측정면적).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>자재</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>PD직경 D(µm)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>R(µm/px)</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>N(자동)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>반복#</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>측정직경(µm)</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>Q_dia(자동)=측정÷PD</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>매칭(Y/N)</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>void%(측정,장비값)</t>
         </is>
       </c>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>기준gold void%</t>
         </is>
       </c>
-      <c r="O5" s="6" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>void편차%(자동)</t>
         </is>
       </c>
-      <c r="P5" s="6" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>판정(자동)</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="7" t="inlineStr">
         <is>
           <t>tact(초)</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
-      <c r="S5" s="6" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>void%σ_rel(자동)</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>총오차_rel(자동)≤0.10</t>
         </is>
       </c>
     </row>
@@ -2748,6 +2839,10 @@
         <f>IFERROR(STDEV(M6:M7)/AVERAGE(M6:M7),"")</f>
         <v/>
       </c>
+      <c r="T6">
+        <f>IFERROR(SQRT(((AVERAGE(M6:M7)-N6)/N6)^2+(2*STDEV(M6:M7)/AVERAGE(M6:M7))^2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2814,7 +2909,7 @@
         <v>55.5</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F8">
         <f>IFERROR(ROUND(C8*0.2828/E8,0),"")</f>
@@ -2843,13 +2938,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>kV55.5×R0.6(N12)</t>
+          <t>kV55.5×R0.5(N15)</t>
         </is>
       </c>
       <c r="S8">
         <f>IFERROR(STDEV(M8:M9)/AVERAGE(M8:M9),"")</f>
         <v/>
       </c>
+      <c r="T8">
+        <f>IFERROR(SQRT(((AVERAGE(M8:M9)-N8)/N8)^2+(2*STDEV(M8:M9)/AVERAGE(M8:M9))^2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2869,7 +2968,7 @@
         <v>55.5</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F9">
         <f>IFERROR(ROUND(C9*0.2828/E9,0),"")</f>
@@ -2952,6 +3051,10 @@
         <f>IFERROR(STDEV(M10:M11)/AVERAGE(M10:M11),"")</f>
         <v/>
       </c>
+      <c r="T10">
+        <f>IFERROR(SQRT(((AVERAGE(M10:M11)-N10)/N10)^2+(2*STDEV(M10:M11)/AVERAGE(M10:M11))^2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3018,7 +3121,7 @@
         <v>59.5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F12">
         <f>IFERROR(ROUND(C12*0.2828/E12,0),"")</f>
@@ -3047,13 +3150,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>kV59.5×R0.6(N12)</t>
+          <t>kV59.5×R0.5(N15)</t>
         </is>
       </c>
       <c r="S12">
         <f>IFERROR(STDEV(M12:M13)/AVERAGE(M12:M13),"")</f>
         <v/>
       </c>
+      <c r="T12">
+        <f>IFERROR(SQRT(((AVERAGE(M12:M13)-N12)/N12)^2+(2*STDEV(M12:M13)/AVERAGE(M12:M13))^2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3073,7 +3180,7 @@
         <v>59.5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F13">
         <f>IFERROR(ROUND(C13*0.2828/E13,0),"")</f>
@@ -3120,7 +3227,7 @@
         <v>60.5</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F14">
         <f>IFERROR(ROUND(C14*0.2828/E14,0),"")</f>
@@ -3156,6 +3263,10 @@
         <f>IFERROR(STDEV(M14:M15)/AVERAGE(M14:M15),"")</f>
         <v/>
       </c>
+      <c r="T14">
+        <f>IFERROR(SQRT(((AVERAGE(M14:M15)-N14)/N14)^2+(2*STDEV(M14:M15)/AVERAGE(M14:M15))^2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3175,7 +3286,7 @@
         <v>60.5</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F15">
         <f>IFERROR(ROUND(C15*0.2828/E15,0),"")</f>
@@ -3222,7 +3333,7 @@
         <v>60.5</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F16">
         <f>IFERROR(ROUND(C16*0.2828/E16,0),"")</f>
@@ -3258,6 +3369,10 @@
         <f>IFERROR(STDEV(M16:M17)/AVERAGE(M16:M17),"")</f>
         <v/>
       </c>
+      <c r="T16">
+        <f>IFERROR(SQRT(((AVERAGE(M16:M17)-N16)/N16)^2+(2*STDEV(M16:M17)/AVERAGE(M16:M17))^2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3277,7 +3392,7 @@
         <v>60.5</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F17">
         <f>IFERROR(ROUND(C17*0.2828/E17,0),"")</f>
@@ -3324,7 +3439,7 @@
         <v>60.5</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F18">
         <f>IFERROR(ROUND(C18*0.2828/E18,0),"")</f>
@@ -3360,6 +3475,10 @@
         <f>IFERROR(STDEV(M18:M19)/AVERAGE(M18:M19),"")</f>
         <v/>
       </c>
+      <c r="T18">
+        <f>IFERROR(SQRT(((AVERAGE(M18:M19)-N18)/N18)^2+(2*STDEV(M18:M19)/AVERAGE(M18:M19))^2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3379,7 +3498,7 @@
         <v>60.5</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F19">
         <f>IFERROR(ROUND(C19*0.2828/E19,0),"")</f>
@@ -3426,7 +3545,7 @@
         <v>60.5</v>
       </c>
       <c r="E20" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F20">
         <f>IFERROR(ROUND(C20*0.2828/E20,0),"")</f>
@@ -3462,6 +3581,10 @@
         <f>IFERROR(STDEV(M20:M21)/AVERAGE(M20:M21),"")</f>
         <v/>
       </c>
+      <c r="T20">
+        <f>IFERROR(SQRT(((AVERAGE(M20:M21)-N20)/N20)^2+(2*STDEV(M20:M21)/AVERAGE(M20:M21))^2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3481,7 +3604,7 @@
         <v>60.5</v>
       </c>
       <c r="E21" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="F21">
         <f>IFERROR(ROUND(C21*0.2828/E21,0),"")</f>
@@ -3525,7 +3648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3545,8 +3668,9 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3557,113 +3681,118 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>모델 산출 (kV,R,F,W)로 자재별 ×3반복. 합격: 매칭Y &amp; Q_dia97~103% &amp; |void편차|≤10% &amp; σ(별도) 최소 &amp; tact 최소.</t>
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>모델 산출 (kV,R,F,W)로 자재별 ×3반복. 합격: 매칭Y &amp; Q_dia97~103% &amp; 총오차_rel≤10%(정확도) &amp; tact 최소.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>D(C열)=PD직경(독립) / 측정직경(J열)=검사결과(종속) / void%(M열)=장비출력(측정면적) / N=20통일 / R≥0.2 · F≥32.</t>
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>정확도=총오차≤10%(픽셀화⊕노이즈). N_target≈29 · R≥0.2 · F≥32. D=PD직경(독립)/측정직경=종속/void%=장비출력(측정면적).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>자재</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>PD직경 D(µm)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>kV</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>R(µm/px)</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>N(자동)</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>반복#</t>
         </is>
       </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>측정직경(µm)</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>Q_dia(자동)=측정÷PD</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="L5" s="7" t="inlineStr">
         <is>
           <t>매칭(Y/N)</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>void%(측정,장비값)</t>
         </is>
       </c>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>기준gold void%</t>
         </is>
       </c>
-      <c r="O5" s="6" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t>void편차%(자동)</t>
         </is>
       </c>
-      <c r="P5" s="6" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>판정(자동)</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="7" t="inlineStr">
         <is>
           <t>tact(초)</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="7" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
-      <c r="S5" s="6" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>void%σ_rel(자동)</t>
+        </is>
+      </c>
+      <c r="T5" s="7" t="inlineStr">
+        <is>
+          <t>총오차_rel(자동)≤0.10</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3817,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(모델R≈0.37)</t>
+          <t>(모델R≈0.25)</t>
         </is>
       </c>
       <c r="F6">
@@ -3722,13 +3851,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>모델 산출값 검증</t>
+          <t>정확도(총오차≤10%) 확인</t>
         </is>
       </c>
       <c r="S6">
         <f>IFERROR(STDEV(M6:M8)/AVERAGE(M6:M8),"")</f>
         <v/>
       </c>
+      <c r="T6">
+        <f>IFERROR(SQRT(((AVERAGE(M6:M8)-N6)/N6)^2+(2*STDEV(M6:M8)/AVERAGE(M6:M8))^2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3751,7 +3884,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(모델R≈0.37)</t>
+          <t>(모델R≈0.25)</t>
         </is>
       </c>
       <c r="F7">
@@ -3806,7 +3939,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(모델R≈0.37)</t>
+          <t>(모델R≈0.25)</t>
         </is>
       </c>
       <c r="F8">
@@ -3861,7 +3994,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(모델R≈2.2)</t>
+          <t>(모델R≈1.5)</t>
         </is>
       </c>
       <c r="F9">
@@ -3895,13 +4028,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>모델 산출값 검증</t>
+          <t>정확도(총오차≤10%) 확인</t>
         </is>
       </c>
       <c r="S9">
         <f>IFERROR(STDEV(M9:M11)/AVERAGE(M9:M11),"")</f>
         <v/>
       </c>
+      <c r="T9">
+        <f>IFERROR(SQRT(((AVERAGE(M9:M11)-N9)/N9)^2+(2*STDEV(M9:M11)/AVERAGE(M9:M11))^2),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3924,7 +4061,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(모델R≈2.2)</t>
+          <t>(모델R≈1.5)</t>
         </is>
       </c>
       <c r="F10">
@@ -3979,7 +4116,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(모델R≈2.2)</t>
+          <t>(모델R≈1.5)</t>
         </is>
       </c>
       <c r="F11">
@@ -4044,12 +4181,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>역설계 모델 — 실험 채우면 계수 확정 → PD직경 D 입력 시 최적 파라미터 산출</t>
+          <t>역설계 모델 — 정확도(총오차≤10%) 만족 설정 중 최소 tact 선택</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>■ 확정할 계수</t>
         </is>
@@ -4061,7 +4198,7 @@
           <t>kV 직경식</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>측정직경/PD=1+s·(kV−kV0). Phase1로 s·kV*</t>
         </is>
@@ -4073,21 +4210,21 @@
           <t>N_target</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>ε=10% 픽셀화 → N=20 통일. Phase1 R스윕 검증</t>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>총오차 예산: 2/N≤~7% → N≈29. Phase1 R스윕·Phase2 σ로 정밀화(총오차≤10% 되는 최대 R)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>F_min</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Phase2 F스윕(32·64·128): 목표 σ 되는 최소 Frame. 장비 하한 32</t>
+          <t>σ(F)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Phase2 F스윕: 2σ≤~7%(σ≤3.5%) 되는 최소 Frame(≥32)</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4234,7 @@
           <t>W*(두꺼운)</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Phase2 W스윕: 깜빡임0·σ최소·블러가드. 얇은=4W</t>
         </is>
@@ -4109,7 +4246,7 @@
           <t>교호작용</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Phase3 kV×R·W×F 계수</t>
         </is>
@@ -4121,16 +4258,16 @@
           <t>tact</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>tact=a·(shot수·F)+b</t>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>tact=a·(shot수·F)+b. 정확도 만족 설정 안에서만 최소화</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>■ 역설계 규칙 (PD직경 D → 파라미터)</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>■ 역설계 규칙 (정확도 우선 → 그 안에서 시간최소)</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4277,7 @@
           <t>입력</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>PD직경 D, void임계 p(8%), (알면)높이 h</t>
         </is>
@@ -4152,9 +4289,9 @@
           <t>1) kV</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>kV*(D)서 시작해 1kV씩 트림→측정직경=PD(100%)</t>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>kV*(D)서 시작 1kV씩 트림→측정직경=PD(100%)</t>
         </is>
       </c>
     </row>
@@ -4164,9 +4301,9 @@
           <t>2) R</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>R = max(0.2, D·√p/20). 26µm는 0.37</t>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>정확도 한계 내 최대 R = min(D√p/N_target, 총오차≤10% 되는 R). 26µm≈0.25·158µm≈1.5, R≥0.2</t>
         </is>
       </c>
     </row>
@@ -4176,9 +4313,9 @@
           <t>3) F</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>max(32, σ목표 되는 최소 Frame). 장비 하한 32</t>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>σ≤목표 되는 최소 F(≥32)</t>
         </is>
       </c>
     </row>
@@ -4188,9 +4325,9 @@
           <t>4) W</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>얇으면 4W, 두꺼우면 W*(D). W↑로 F↓ 교환(단 32까지)</t>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>얇으면 4W, 두꺼우면 W*(D). 블러 가드 내에서 W↑로 F↓ 교환</t>
         </is>
       </c>
     </row>
@@ -4200,16 +4337,16 @@
           <t>5) 검증</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>tact·합격기준 확인, 미달 시 해당 변수만 재조정</t>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>총오차≤10% &amp; 매칭 &amp; Q_dia 확인 후 tact 계산. 미달이면 정확도 우선으로 R↓·F↑</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>※ 확정 계수는 레시피모델.xlsx·파라미터_계산기.xlsx 보정계수·N_target(=20)에 옮겨 완성.</t>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>※ 정확도가 설정을 고정하면 시간여유가 적어도 그대로 둔다(정확도&gt;시간). 확정 계수는 레시피모델·계산기에 반영.</t>
         </is>
       </c>
     </row>
